--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD297"/>
+  <dimension ref="A1:AD298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28720,7 +28720,7 @@
         <v>386.69</v>
       </c>
       <c r="D297" t="n">
-        <v>353.02</v>
+        <v>373.5</v>
       </c>
       <c r="E297" t="n">
         <v>388.85</v>
@@ -28798,6 +28798,102 @@
         <v>371.17</v>
       </c>
       <c r="AD297" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>399.26</v>
+      </c>
+      <c r="C298" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="D298" t="n">
+        <v>404.75</v>
+      </c>
+      <c r="E298" t="n">
+        <v>391.67</v>
+      </c>
+      <c r="F298" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="G298" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="H298" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="I298" t="n">
+        <v>374.54</v>
+      </c>
+      <c r="J298" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="K298" t="n">
+        <v>356.69</v>
+      </c>
+      <c r="L298" t="n">
+        <v>358.85</v>
+      </c>
+      <c r="M298" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="N298" t="n">
+        <v>352.21</v>
+      </c>
+      <c r="O298" t="n">
+        <v>353.74</v>
+      </c>
+      <c r="P298" t="n">
+        <v>355.91</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="R298" t="n">
+        <v>352.28</v>
+      </c>
+      <c r="S298" t="n">
+        <v>356.21</v>
+      </c>
+      <c r="T298" t="n">
+        <v>358.93</v>
+      </c>
+      <c r="U298" t="n">
+        <v>357.51</v>
+      </c>
+      <c r="V298" t="n">
+        <v>343.83</v>
+      </c>
+      <c r="W298" t="n">
+        <v>349.56</v>
+      </c>
+      <c r="X298" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>369.01</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>351.22</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="AD298" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28814,7 +28910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B314"/>
+  <dimension ref="A1:B315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31957,6 +32053,16 @@
       </c>
       <c r="B314" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -32125,28 +32231,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.097091507851723</v>
+        <v>-7.078520891345231</v>
       </c>
       <c r="J2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K2" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7754847401957576</v>
+        <v>0.775594757996047</v>
       </c>
       <c r="M2" t="n">
-        <v>19.41769001666552</v>
+        <v>19.4228610318436</v>
       </c>
       <c r="N2" t="n">
-        <v>694.1434144297267</v>
+        <v>693.4869464021399</v>
       </c>
       <c r="O2" t="n">
-        <v>26.34660157268346</v>
+        <v>26.334140320165</v>
       </c>
       <c r="P2" t="n">
-        <v>562.4644748115791</v>
+        <v>562.2575139176807</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32207,28 +32313,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.768511006591865</v>
+        <v>-3.758556811397403</v>
       </c>
       <c r="J3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4808354493401442</v>
+        <v>0.4814723908271638</v>
       </c>
       <c r="M3" t="n">
-        <v>22.63074564856156</v>
+        <v>22.5940091288619</v>
       </c>
       <c r="N3" t="n">
-        <v>797.2897752950643</v>
+        <v>795.0112408090804</v>
       </c>
       <c r="O3" t="n">
-        <v>28.23632014436485</v>
+        <v>28.19594369424582</v>
       </c>
       <c r="P3" t="n">
-        <v>487.5498922075556</v>
+        <v>487.4463294576066</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32285,28 +32391,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.260449646124704</v>
+        <v>2.265865327809518</v>
       </c>
       <c r="J4" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K4" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1731831105841439</v>
+        <v>0.175966263266904</v>
       </c>
       <c r="M4" t="n">
-        <v>29.77212146022963</v>
+        <v>29.62924202088931</v>
       </c>
       <c r="N4" t="n">
-        <v>1280.909132713071</v>
+        <v>1268.484100903831</v>
       </c>
       <c r="O4" t="n">
-        <v>35.78979090066147</v>
+        <v>35.61578443476755</v>
       </c>
       <c r="P4" t="n">
-        <v>358.6265230931405</v>
+        <v>358.5711015445283</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32363,28 +32469,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.814250244700111</v>
+        <v>1.808162165376606</v>
       </c>
       <c r="J5" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5657987769768877</v>
+        <v>0.5657717904763244</v>
       </c>
       <c r="M5" t="n">
-        <v>8.978112874986849</v>
+        <v>8.972425594515595</v>
       </c>
       <c r="N5" t="n">
-        <v>128.2341039244876</v>
+        <v>128.0198859605287</v>
       </c>
       <c r="O5" t="n">
-        <v>11.32404980227867</v>
+        <v>11.3145873084496</v>
       </c>
       <c r="P5" t="n">
-        <v>352.2537094957322</v>
+        <v>352.3176752460845</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32441,28 +32547,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7128822845072047</v>
+        <v>0.7122209929073136</v>
       </c>
       <c r="J6" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K6" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3994451920779877</v>
+        <v>0.4009878885190566</v>
       </c>
       <c r="M6" t="n">
-        <v>3.230626877894682</v>
+        <v>3.222324579342022</v>
       </c>
       <c r="N6" t="n">
-        <v>38.53869472191121</v>
+        <v>38.41025380625458</v>
       </c>
       <c r="O6" t="n">
-        <v>6.207954149469148</v>
+        <v>6.197600649142745</v>
       </c>
       <c r="P6" t="n">
-        <v>363.8032731788536</v>
+        <v>363.8102450599741</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32519,28 +32625,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2434683134800316</v>
+        <v>0.2438622381186235</v>
       </c>
       <c r="J7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K7" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0278331713257215</v>
+        <v>0.02814550216092115</v>
       </c>
       <c r="M7" t="n">
-        <v>4.299720919502595</v>
+        <v>4.286184562883169</v>
       </c>
       <c r="N7" t="n">
-        <v>106.2950665548766</v>
+        <v>105.9344843391457</v>
       </c>
       <c r="O7" t="n">
-        <v>10.309949881298</v>
+        <v>10.29244792744397</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8408963552253</v>
+        <v>376.8367830310463</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32597,28 +32703,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0298186726320801</v>
+        <v>0.03062726316437785</v>
       </c>
       <c r="J8" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K8" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005284363261048863</v>
+        <v>0.0005620517389685054</v>
       </c>
       <c r="M8" t="n">
-        <v>6.119409574796461</v>
+        <v>6.101664060165138</v>
       </c>
       <c r="N8" t="n">
-        <v>86.81420732477442</v>
+        <v>86.52402037267062</v>
       </c>
       <c r="O8" t="n">
-        <v>9.317414197339003</v>
+        <v>9.301828872467533</v>
       </c>
       <c r="P8" t="n">
-        <v>373.0622368673696</v>
+        <v>373.0538329041572</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32675,28 +32781,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02860392909976098</v>
+        <v>-0.02501912011454407</v>
       </c>
       <c r="J9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003186034446248653</v>
+        <v>0.0002456396853459664</v>
       </c>
       <c r="M9" t="n">
-        <v>7.93258018903018</v>
+        <v>7.921362067864469</v>
       </c>
       <c r="N9" t="n">
-        <v>133.3806710675561</v>
+        <v>133.006323091383</v>
       </c>
       <c r="O9" t="n">
-        <v>11.54905498590928</v>
+        <v>11.53283673219139</v>
       </c>
       <c r="P9" t="n">
-        <v>370.3934887882993</v>
+        <v>370.3563618515726</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32753,28 +32859,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3616840108906128</v>
+        <v>-0.3601227771772292</v>
       </c>
       <c r="J10" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K10" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L10" t="n">
-        <v>0.047111704211109</v>
+        <v>0.04709119727809274</v>
       </c>
       <c r="M10" t="n">
-        <v>8.34980766445234</v>
+        <v>8.328973158199124</v>
       </c>
       <c r="N10" t="n">
-        <v>134.9332601180101</v>
+        <v>134.4908355153648</v>
       </c>
       <c r="O10" t="n">
-        <v>11.61607765633521</v>
+        <v>11.59701838902417</v>
       </c>
       <c r="P10" t="n">
-        <v>366.0557694984276</v>
+        <v>366.0394339687929</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32831,28 +32937,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02525900121362785</v>
+        <v>-0.02363816721111688</v>
       </c>
       <c r="J11" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K11" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003674075094781681</v>
+        <v>0.0003244162605907652</v>
       </c>
       <c r="M11" t="n">
-        <v>6.240822322855119</v>
+        <v>6.228979588069128</v>
       </c>
       <c r="N11" t="n">
-        <v>87.596296226853</v>
+        <v>87.31324963518425</v>
       </c>
       <c r="O11" t="n">
-        <v>9.359289301376092</v>
+        <v>9.344155908116273</v>
       </c>
       <c r="P11" t="n">
-        <v>355.1799557212851</v>
+        <v>355.1628442355631</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32909,28 +33015,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1232762149470836</v>
+        <v>0.1263596536671335</v>
       </c>
       <c r="J12" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K12" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02363354514292704</v>
+        <v>0.02495537786585134</v>
       </c>
       <c r="M12" t="n">
-        <v>4.37432609861194</v>
+        <v>4.374428410455061</v>
       </c>
       <c r="N12" t="n">
-        <v>32.72944585441807</v>
+        <v>32.67961292592913</v>
       </c>
       <c r="O12" t="n">
-        <v>5.720965465235572</v>
+        <v>5.716608516063448</v>
       </c>
       <c r="P12" t="n">
-        <v>351.3541064392436</v>
+        <v>351.3223376867138</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32987,28 +33093,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2263686197233826</v>
+        <v>0.2254289818714644</v>
       </c>
       <c r="J13" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K13" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1162633634420708</v>
+        <v>0.1162243610161715</v>
       </c>
       <c r="M13" t="n">
-        <v>3.439998202792007</v>
+        <v>3.432189009663444</v>
       </c>
       <c r="N13" t="n">
-        <v>20.30525812728327</v>
+        <v>20.24249623529308</v>
       </c>
       <c r="O13" t="n">
-        <v>4.506135609064963</v>
+        <v>4.499166171113608</v>
       </c>
       <c r="P13" t="n">
-        <v>348.2404829170164</v>
+        <v>348.2501640312189</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33065,28 +33171,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1567755375162765</v>
+        <v>0.1561052861905567</v>
       </c>
       <c r="J14" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K14" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05690211388455668</v>
+        <v>0.05687597929914445</v>
       </c>
       <c r="M14" t="n">
-        <v>3.662531874579349</v>
+        <v>3.653615820814412</v>
       </c>
       <c r="N14" t="n">
-        <v>21.23640798014715</v>
+        <v>21.16775729349173</v>
       </c>
       <c r="O14" t="n">
-        <v>4.608297731282902</v>
+        <v>4.600843106811157</v>
       </c>
       <c r="P14" t="n">
-        <v>349.0229709652489</v>
+        <v>349.029876582786</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33143,28 +33249,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2988340113849191</v>
+        <v>0.2964476897647765</v>
       </c>
       <c r="J15" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K15" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1985571933621624</v>
+        <v>0.1970106290891348</v>
       </c>
       <c r="M15" t="n">
-        <v>3.399981220602891</v>
+        <v>3.399394855241423</v>
       </c>
       <c r="N15" t="n">
-        <v>18.79070399837018</v>
+        <v>18.76359231322431</v>
       </c>
       <c r="O15" t="n">
-        <v>4.334824563736135</v>
+        <v>4.3316962397223</v>
       </c>
       <c r="P15" t="n">
-        <v>349.2037856538957</v>
+        <v>349.2283719900904</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33221,28 +33327,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3649884929962588</v>
+        <v>0.361378840162663</v>
       </c>
       <c r="J16" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K16" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2586735028861293</v>
+        <v>0.2556507442943999</v>
       </c>
       <c r="M16" t="n">
-        <v>3.227506044832642</v>
+        <v>3.235699528295514</v>
       </c>
       <c r="N16" t="n">
-        <v>19.9027009135464</v>
+        <v>19.91841815166596</v>
       </c>
       <c r="O16" t="n">
-        <v>4.461244323453537</v>
+        <v>4.463005506569083</v>
       </c>
       <c r="P16" t="n">
-        <v>351.3215486520936</v>
+        <v>351.3587390028677</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33299,28 +33405,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.472420006586722</v>
+        <v>0.4691978963630669</v>
       </c>
       <c r="J17" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K17" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3697706842039901</v>
+        <v>0.3677220382440434</v>
       </c>
       <c r="M17" t="n">
-        <v>3.344902054889812</v>
+        <v>3.348937752793982</v>
       </c>
       <c r="N17" t="n">
-        <v>19.82982032216713</v>
+        <v>19.82897236433833</v>
       </c>
       <c r="O17" t="n">
-        <v>4.453068641079668</v>
+        <v>4.452973429556742</v>
       </c>
       <c r="P17" t="n">
-        <v>350.8046676946778</v>
+        <v>350.8378651834599</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33377,28 +33483,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5741949603678758</v>
+        <v>0.5677094484897602</v>
       </c>
       <c r="J18" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K18" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4553076032150712</v>
+        <v>0.448508653287525</v>
       </c>
       <c r="M18" t="n">
-        <v>3.562586837371276</v>
+        <v>3.58596979390912</v>
       </c>
       <c r="N18" t="n">
-        <v>20.56180592098628</v>
+        <v>20.75964055363928</v>
       </c>
       <c r="O18" t="n">
-        <v>4.534512754529012</v>
+        <v>4.556274854926914</v>
       </c>
       <c r="P18" t="n">
-        <v>346.1863132272865</v>
+        <v>346.2531336315791</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33455,28 +33561,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5908977937786213</v>
+        <v>0.5862458732779561</v>
       </c>
       <c r="J19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4133921833984815</v>
+        <v>0.410263941351346</v>
       </c>
       <c r="M19" t="n">
-        <v>4.069191530769931</v>
+        <v>4.081795412582079</v>
       </c>
       <c r="N19" t="n">
-        <v>25.82892994786977</v>
+        <v>25.87936651486837</v>
       </c>
       <c r="O19" t="n">
-        <v>5.082217030772079</v>
+        <v>5.087176674233791</v>
       </c>
       <c r="P19" t="n">
-        <v>347.140827276126</v>
+        <v>347.1887561388639</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33533,28 +33639,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6038152193827682</v>
+        <v>0.5972759160925892</v>
       </c>
       <c r="J20" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K20" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3830215671330303</v>
+        <v>0.3777373004272897</v>
       </c>
       <c r="M20" t="n">
-        <v>4.47342875548601</v>
+        <v>4.495444057613712</v>
       </c>
       <c r="N20" t="n">
-        <v>30.61617680886512</v>
+        <v>30.78460685619434</v>
       </c>
       <c r="O20" t="n">
-        <v>5.533188665576579</v>
+        <v>5.548387770892941</v>
       </c>
       <c r="P20" t="n">
-        <v>352.1340366681403</v>
+        <v>352.2014112868063</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33611,28 +33717,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6583177042148235</v>
+        <v>0.647618314870699</v>
       </c>
       <c r="J21" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K21" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3862349824901337</v>
+        <v>0.3757017799970229</v>
       </c>
       <c r="M21" t="n">
-        <v>5.068435754119919</v>
+        <v>5.108578179321039</v>
       </c>
       <c r="N21" t="n">
-        <v>35.90192098600691</v>
+        <v>36.50789539621761</v>
       </c>
       <c r="O21" t="n">
-        <v>5.991821174401561</v>
+        <v>6.042176379105265</v>
       </c>
       <c r="P21" t="n">
-        <v>355.0285661214548</v>
+        <v>355.1388022192516</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33689,28 +33795,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5821415117864853</v>
+        <v>0.5650431938342652</v>
       </c>
       <c r="J22" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K22" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2388613429103473</v>
+        <v>0.2239336686098347</v>
       </c>
       <c r="M22" t="n">
-        <v>6.433476550688724</v>
+        <v>6.507106381252894</v>
       </c>
       <c r="N22" t="n">
-        <v>56.29517079930066</v>
+        <v>57.96187855778443</v>
       </c>
       <c r="O22" t="n">
-        <v>7.503010782299374</v>
+        <v>7.613269899181589</v>
       </c>
       <c r="P22" t="n">
-        <v>352.1839987722866</v>
+        <v>352.3601632046033</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33767,28 +33873,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>1.005409288804561</v>
+        <v>0.9913094325408143</v>
       </c>
       <c r="J23" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K23" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L23" t="n">
-        <v>0.551167866372306</v>
+        <v>0.5389888293138951</v>
       </c>
       <c r="M23" t="n">
-        <v>5.337077352719498</v>
+        <v>5.391952043136734</v>
       </c>
       <c r="N23" t="n">
-        <v>42.91231372279447</v>
+        <v>44.03012015644725</v>
       </c>
       <c r="O23" t="n">
-        <v>6.550749096309099</v>
+        <v>6.635519584512373</v>
       </c>
       <c r="P23" t="n">
-        <v>342.6753999120206</v>
+        <v>342.8206711124621</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33845,28 +33951,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6868622429391208</v>
+        <v>0.6826789956407437</v>
       </c>
       <c r="J24" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K24" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4143404162473582</v>
+        <v>0.4125935026582198</v>
       </c>
       <c r="M24" t="n">
-        <v>4.90846596686988</v>
+        <v>4.912724784407515</v>
       </c>
       <c r="N24" t="n">
-        <v>34.76348729984974</v>
+        <v>34.75754967397084</v>
       </c>
       <c r="O24" t="n">
-        <v>5.896056928138478</v>
+        <v>5.895553381487681</v>
       </c>
       <c r="P24" t="n">
-        <v>354.1600274307751</v>
+        <v>354.2031275408338</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33923,28 +34029,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7335423003126348</v>
+        <v>0.7251616292751006</v>
       </c>
       <c r="J25" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K25" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4640077704602746</v>
+        <v>0.4569324388704864</v>
       </c>
       <c r="M25" t="n">
-        <v>4.751388455069341</v>
+        <v>4.769206051291</v>
       </c>
       <c r="N25" t="n">
-        <v>32.40258496931276</v>
+        <v>32.73943740500646</v>
       </c>
       <c r="O25" t="n">
-        <v>5.692326850182864</v>
+        <v>5.721838638497809</v>
       </c>
       <c r="P25" t="n">
-        <v>361.3562138459823</v>
+        <v>361.4425601263524</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34001,28 +34107,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6249755103320239</v>
+        <v>0.6162214896348502</v>
       </c>
       <c r="J26" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K26" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4145654483192394</v>
+        <v>0.4056554065574146</v>
       </c>
       <c r="M26" t="n">
-        <v>4.267309284692729</v>
+        <v>4.297379811828608</v>
       </c>
       <c r="N26" t="n">
-        <v>28.75460056666399</v>
+        <v>29.14435416116193</v>
       </c>
       <c r="O26" t="n">
-        <v>5.362331635274342</v>
+        <v>5.398551116842549</v>
       </c>
       <c r="P26" t="n">
-        <v>346.9232556323644</v>
+        <v>347.0134485443756</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34079,28 +34185,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4281686872160964</v>
+        <v>0.4209952109192232</v>
       </c>
       <c r="J27" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K27" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2755265959658431</v>
+        <v>0.2679011576534844</v>
       </c>
       <c r="M27" t="n">
-        <v>3.867286472590135</v>
+        <v>3.893817794573786</v>
       </c>
       <c r="N27" t="n">
-        <v>25.1295562188574</v>
+        <v>25.37167559397117</v>
       </c>
       <c r="O27" t="n">
-        <v>5.012938880423079</v>
+        <v>5.037030434092211</v>
       </c>
       <c r="P27" t="n">
-        <v>344.8750043715403</v>
+        <v>344.9489128918466</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34157,28 +34263,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2597929406090252</v>
+        <v>0.2533872083838487</v>
       </c>
       <c r="J28" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K28" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1146717062782318</v>
+        <v>0.1095663225472927</v>
       </c>
       <c r="M28" t="n">
-        <v>4.038280680403724</v>
+        <v>4.056089276430469</v>
       </c>
       <c r="N28" t="n">
-        <v>27.16432094030647</v>
+        <v>27.33339481696735</v>
       </c>
       <c r="O28" t="n">
-        <v>5.211940228005926</v>
+        <v>5.228134927196059</v>
       </c>
       <c r="P28" t="n">
-        <v>360.5815056715238</v>
+        <v>360.6475041038944</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34235,28 +34341,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1283674700288712</v>
+        <v>0.1247454460400091</v>
       </c>
       <c r="J29" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K29" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L29" t="n">
-        <v>0.04264768017073783</v>
+        <v>0.04052175641961853</v>
       </c>
       <c r="M29" t="n">
-        <v>3.286485020404682</v>
+        <v>3.294791772111008</v>
       </c>
       <c r="N29" t="n">
-        <v>19.2833479344376</v>
+        <v>19.30171857733167</v>
       </c>
       <c r="O29" t="n">
-        <v>4.391280899058679</v>
+        <v>4.393372119150809</v>
       </c>
       <c r="P29" t="n">
-        <v>372.0747851539757</v>
+        <v>372.1121029650971</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34294,7 +34400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD297"/>
+  <dimension ref="A1:AD298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78915,7 +79021,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>-36.669392565557814,175.556653001751</t>
+          <t>-36.66945447817194,175.5568687606071</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -79044,6 +79150,158 @@
         </is>
       </c>
       <c r="AD297" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>-36.66818366833069,175.55777311571993</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>-36.66886544978971,175.55748254669214</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>-36.66954894854262,175.55719798312214</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-36.67018374001905,175.5567436977633</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-36.67082765474737,175.55632122683332</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-36.671486229205655,175.55603395683562</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-36.67216284635221,175.5558131512061</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-36.67287649086055,175.5557066733714</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-36.673578605906656,175.55542824306465</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-36.67429270727157,175.55530399396667</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-36.675010404274225,175.5552260558863</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-36.67572209418398,175.55505731318956</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-36.676440809123356,175.55497530745754</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-36.6771598946753,175.55492017196414</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-36.67788088732485,175.554871665794</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-36.678600222129205,175.55490298107566</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-36.679324575129506,175.55492878997802</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>-36.680036261664924,175.55507027210317</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>-36.68074963149854,175.5551981922181</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>-36.68146386020645,175.5553191726924</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>-36.6821951573279,175.55540355337226</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>-36.68287709312709,175.55569666850053</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>-36.68353161776119,175.55610919132445</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>-36.68420833364713,175.55636153431422</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>-36.68487382049589,175.55671691464795</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>-36.685473177271355,175.5572231880681</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>-36.685975617882754,175.55788199921227</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>-36.68629743739381,175.55868485306178</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD298"/>
+  <dimension ref="A1:AD300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28894,6 +28894,198 @@
         <v>370.44</v>
       </c>
       <c r="AD298" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:06:07+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>405.08</v>
+      </c>
+      <c r="C299" t="n">
+        <v>404.72</v>
+      </c>
+      <c r="D299" t="n">
+        <v>410.44</v>
+      </c>
+      <c r="E299" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="F299" t="n">
+        <v>380.81</v>
+      </c>
+      <c r="G299" t="n">
+        <v>384.07</v>
+      </c>
+      <c r="H299" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="I299" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="J299" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="K299" t="n">
+        <v>357.97</v>
+      </c>
+      <c r="L299" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="M299" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="N299" t="n">
+        <v>351.93</v>
+      </c>
+      <c r="O299" t="n">
+        <v>353.74</v>
+      </c>
+      <c r="P299" t="n">
+        <v>355.91</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="R299" t="n">
+        <v>352.28</v>
+      </c>
+      <c r="S299" t="n">
+        <v>356.21</v>
+      </c>
+      <c r="T299" t="n">
+        <v>358.93</v>
+      </c>
+      <c r="U299" t="n">
+        <v>357.51</v>
+      </c>
+      <c r="V299" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="W299" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="X299" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>358.87</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>417.17</v>
+      </c>
+      <c r="C300" t="n">
+        <v>407.05</v>
+      </c>
+      <c r="D300" t="n">
+        <v>424.38</v>
+      </c>
+      <c r="E300" t="n">
+        <v>392.08</v>
+      </c>
+      <c r="F300" t="n">
+        <v>381.22</v>
+      </c>
+      <c r="G300" t="n">
+        <v>384.67</v>
+      </c>
+      <c r="H300" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="I300" t="n">
+        <v>377.4</v>
+      </c>
+      <c r="J300" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="K300" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="L300" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="M300" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="N300" t="n">
+        <v>352.53</v>
+      </c>
+      <c r="O300" t="n">
+        <v>353.72</v>
+      </c>
+      <c r="P300" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="R300" t="n">
+        <v>357.68</v>
+      </c>
+      <c r="S300" t="n">
+        <v>362.12</v>
+      </c>
+      <c r="T300" t="n">
+        <v>366.66</v>
+      </c>
+      <c r="U300" t="n">
+        <v>367.54</v>
+      </c>
+      <c r="V300" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="W300" t="n">
+        <v>366.65</v>
+      </c>
+      <c r="X300" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>348.11</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>360.64</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>370.35</v>
+      </c>
+      <c r="AD300" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28910,7 +29102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B315"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32063,6 +32255,26 @@
       </c>
       <c r="B315" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -32231,28 +32443,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.078520891345231</v>
+        <v>-7.022793875439326</v>
       </c>
       <c r="J2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K2" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L2" t="n">
-        <v>0.775594757996047</v>
+        <v>0.7735439478474904</v>
       </c>
       <c r="M2" t="n">
-        <v>19.4228610318436</v>
+        <v>19.51018005686012</v>
       </c>
       <c r="N2" t="n">
-        <v>693.4869464021399</v>
+        <v>697.4049080246582</v>
       </c>
       <c r="O2" t="n">
-        <v>26.334140320165</v>
+        <v>26.40842494403364</v>
       </c>
       <c r="P2" t="n">
-        <v>562.2575139176807</v>
+        <v>561.6347978551671</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32313,28 +32525,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.758556811397403</v>
+        <v>-3.732583622547929</v>
       </c>
       <c r="J3" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K3" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4814723908271638</v>
+        <v>0.4815919871436227</v>
       </c>
       <c r="M3" t="n">
-        <v>22.5940091288619</v>
+        <v>22.54780163575558</v>
       </c>
       <c r="N3" t="n">
-        <v>795.0112408090804</v>
+        <v>791.400381401898</v>
       </c>
       <c r="O3" t="n">
-        <v>28.19594369424582</v>
+        <v>28.13183928224207</v>
       </c>
       <c r="P3" t="n">
-        <v>487.4463294576066</v>
+        <v>487.1753703347477</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32391,28 +32603,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.265865327809518</v>
+        <v>2.264800482680998</v>
       </c>
       <c r="J4" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K4" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L4" t="n">
-        <v>0.175966263266904</v>
+        <v>0.1782416180759679</v>
       </c>
       <c r="M4" t="n">
-        <v>29.62924202088931</v>
+        <v>29.46191020883406</v>
       </c>
       <c r="N4" t="n">
-        <v>1268.484100903831</v>
+        <v>1259.446674704517</v>
       </c>
       <c r="O4" t="n">
-        <v>35.61578443476755</v>
+        <v>35.48868375559337</v>
       </c>
       <c r="P4" t="n">
-        <v>358.5711015445283</v>
+        <v>358.5821672783029</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32469,28 +32681,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.808162165376606</v>
+        <v>1.796050157251418</v>
       </c>
       <c r="J5" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K5" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5657717904763244</v>
+        <v>0.5656621418715462</v>
       </c>
       <c r="M5" t="n">
-        <v>8.972425594515595</v>
+        <v>8.961787120022674</v>
       </c>
       <c r="N5" t="n">
-        <v>128.0198859605287</v>
+        <v>127.6030696068365</v>
       </c>
       <c r="O5" t="n">
-        <v>11.3145873084496</v>
+        <v>11.29615286754019</v>
       </c>
       <c r="P5" t="n">
-        <v>352.3176752460845</v>
+        <v>352.4452528491931</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32547,28 +32759,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7122209929073136</v>
+        <v>0.7100011151433874</v>
       </c>
       <c r="J6" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K6" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4009878885190566</v>
+        <v>0.4033624286200765</v>
       </c>
       <c r="M6" t="n">
-        <v>3.222324579342022</v>
+        <v>3.209514904443327</v>
       </c>
       <c r="N6" t="n">
-        <v>38.41025380625458</v>
+        <v>38.16612783104744</v>
       </c>
       <c r="O6" t="n">
-        <v>6.197600649142745</v>
+        <v>6.177874054320583</v>
       </c>
       <c r="P6" t="n">
-        <v>363.8102450599741</v>
+        <v>363.8337057555415</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32625,28 +32837,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2438622381186235</v>
+        <v>0.2454885254057575</v>
       </c>
       <c r="J7" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K7" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02814550216092115</v>
+        <v>0.02896501176789579</v>
       </c>
       <c r="M7" t="n">
-        <v>4.286184562883169</v>
+        <v>4.261636056657993</v>
       </c>
       <c r="N7" t="n">
-        <v>105.9344843391457</v>
+        <v>105.2276377798047</v>
       </c>
       <c r="O7" t="n">
-        <v>10.29244792744397</v>
+        <v>10.25805233851947</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8367830310463</v>
+        <v>376.8197535293706</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32703,28 +32915,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03062726316437785</v>
+        <v>0.03866732985868792</v>
       </c>
       <c r="J8" t="n">
+        <v>299</v>
+      </c>
+      <c r="K8" t="n">
         <v>297</v>
       </c>
-      <c r="K8" t="n">
-        <v>295</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0005620517389685054</v>
+        <v>0.0009078079330687716</v>
       </c>
       <c r="M8" t="n">
-        <v>6.101664060165138</v>
+        <v>6.089922943584225</v>
       </c>
       <c r="N8" t="n">
-        <v>86.52402037267062</v>
+        <v>86.17634506863529</v>
       </c>
       <c r="O8" t="n">
-        <v>9.301828872467533</v>
+        <v>9.283121515343602</v>
       </c>
       <c r="P8" t="n">
-        <v>373.0538329041572</v>
+        <v>372.9700244696094</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32781,28 +32993,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02501912011454407</v>
+        <v>-0.01438480338247265</v>
       </c>
       <c r="J9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K9" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002456396853459664</v>
+        <v>8.232696696175434e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.921362067864469</v>
+        <v>7.91515003568054</v>
       </c>
       <c r="N9" t="n">
-        <v>133.006323091383</v>
+        <v>132.4669248608263</v>
       </c>
       <c r="O9" t="n">
-        <v>11.53283673219139</v>
+        <v>11.50942765131378</v>
       </c>
       <c r="P9" t="n">
-        <v>370.3563618515726</v>
+        <v>370.2459316059758</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32859,28 +33071,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3601227771772292</v>
+        <v>-0.3535434814156669</v>
       </c>
       <c r="J10" t="n">
+        <v>299</v>
+      </c>
+      <c r="K10" t="n">
         <v>297</v>
       </c>
-      <c r="K10" t="n">
-        <v>295</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.04709119727809274</v>
+        <v>0.04613512732844505</v>
       </c>
       <c r="M10" t="n">
-        <v>8.328973158199124</v>
+        <v>8.303936917745203</v>
       </c>
       <c r="N10" t="n">
-        <v>134.4908355153648</v>
+        <v>133.7283819311802</v>
       </c>
       <c r="O10" t="n">
-        <v>11.59701838902417</v>
+        <v>11.56409883783342</v>
       </c>
       <c r="P10" t="n">
-        <v>366.0394339687929</v>
+        <v>365.970402080903</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32937,28 +33149,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02363816721111688</v>
+        <v>-0.01772327595144314</v>
       </c>
       <c r="J11" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K11" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003244162605907652</v>
+        <v>0.0001851970467747766</v>
       </c>
       <c r="M11" t="n">
-        <v>6.228979588069128</v>
+        <v>6.221245773221479</v>
       </c>
       <c r="N11" t="n">
-        <v>87.31324963518425</v>
+        <v>86.83142807012733</v>
       </c>
       <c r="O11" t="n">
-        <v>9.344155908116273</v>
+        <v>9.31833826763803</v>
       </c>
       <c r="P11" t="n">
-        <v>355.1628442355631</v>
+        <v>355.1002320017382</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33015,28 +33227,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1263596536671335</v>
+        <v>0.1281711134962176</v>
       </c>
       <c r="J12" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K12" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02495537786585134</v>
+        <v>0.02605831928872959</v>
       </c>
       <c r="M12" t="n">
-        <v>4.374428410455061</v>
+        <v>4.353975565953416</v>
       </c>
       <c r="N12" t="n">
-        <v>32.67961292592913</v>
+        <v>32.47226932831133</v>
       </c>
       <c r="O12" t="n">
-        <v>5.716608516063448</v>
+        <v>5.698444465668795</v>
       </c>
       <c r="P12" t="n">
-        <v>351.3223376867138</v>
+        <v>351.3036293720355</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33093,28 +33305,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2254289818714644</v>
+        <v>0.222256943515189</v>
       </c>
       <c r="J13" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K13" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1162243610161715</v>
+        <v>0.1148145588560114</v>
       </c>
       <c r="M13" t="n">
-        <v>3.432189009663444</v>
+        <v>3.422140291423021</v>
       </c>
       <c r="N13" t="n">
-        <v>20.24249623529308</v>
+        <v>20.14158997802371</v>
       </c>
       <c r="O13" t="n">
-        <v>4.499166171113608</v>
+        <v>4.487938276984623</v>
       </c>
       <c r="P13" t="n">
-        <v>348.2501640312189</v>
+        <v>348.28293840895</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33171,28 +33383,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1561052861905567</v>
+        <v>0.1548224320692007</v>
       </c>
       <c r="J14" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K14" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05687597929914445</v>
+        <v>0.05684776081940568</v>
       </c>
       <c r="M14" t="n">
-        <v>3.653615820814412</v>
+        <v>3.635642835081201</v>
       </c>
       <c r="N14" t="n">
-        <v>21.16775729349173</v>
+        <v>21.03206826641504</v>
       </c>
       <c r="O14" t="n">
-        <v>4.600843106811157</v>
+        <v>4.586073294923996</v>
       </c>
       <c r="P14" t="n">
-        <v>349.029876582786</v>
+        <v>349.0431246154865</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33249,28 +33461,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2964476897647765</v>
+        <v>0.2917641048031678</v>
       </c>
       <c r="J15" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K15" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1970106290891348</v>
+        <v>0.1939623524318667</v>
       </c>
       <c r="M15" t="n">
-        <v>3.399394855241423</v>
+        <v>3.397796104931616</v>
       </c>
       <c r="N15" t="n">
-        <v>18.76359231322431</v>
+        <v>18.70886234642364</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3316962397223</v>
+        <v>4.325374243510455</v>
       </c>
       <c r="P15" t="n">
-        <v>349.2283719900904</v>
+        <v>349.2767536665127</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33327,28 +33539,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.361378840162663</v>
+        <v>0.3549660831623034</v>
       </c>
       <c r="J16" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K16" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2556507442943999</v>
+        <v>0.2506778793365679</v>
       </c>
       <c r="M16" t="n">
-        <v>3.235699528295514</v>
+        <v>3.247720586592378</v>
       </c>
       <c r="N16" t="n">
-        <v>19.91841815166596</v>
+        <v>19.91920645891008</v>
       </c>
       <c r="O16" t="n">
-        <v>4.463005506569083</v>
+        <v>4.463093821432626</v>
       </c>
       <c r="P16" t="n">
-        <v>351.3587390028677</v>
+        <v>351.4249770695727</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33405,28 +33617,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4691978963630669</v>
+        <v>0.4641925211244187</v>
       </c>
       <c r="J17" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K17" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3677220382440434</v>
+        <v>0.3655004860160029</v>
       </c>
       <c r="M17" t="n">
-        <v>3.348937752793982</v>
+        <v>3.350483308233973</v>
       </c>
       <c r="N17" t="n">
-        <v>19.82897236433833</v>
+        <v>19.78269191921518</v>
       </c>
       <c r="O17" t="n">
-        <v>4.452973429556742</v>
+        <v>4.44777381610342</v>
       </c>
       <c r="P17" t="n">
-        <v>350.8378651834599</v>
+        <v>350.8895589656728</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33483,28 +33695,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5677094484897602</v>
+        <v>0.5589039984501559</v>
       </c>
       <c r="J18" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K18" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L18" t="n">
-        <v>0.448508653287525</v>
+        <v>0.4412484380732926</v>
       </c>
       <c r="M18" t="n">
-        <v>3.58596979390912</v>
+        <v>3.609512299797915</v>
       </c>
       <c r="N18" t="n">
-        <v>20.75964055363928</v>
+        <v>20.91971564327567</v>
       </c>
       <c r="O18" t="n">
-        <v>4.556274854926914</v>
+        <v>4.573807565177581</v>
       </c>
       <c r="P18" t="n">
-        <v>346.2531336315791</v>
+        <v>346.3440589210293</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33561,28 +33773,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5862458732779561</v>
+        <v>0.5813644482648999</v>
       </c>
       <c r="J19" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K19" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L19" t="n">
-        <v>0.410263941351346</v>
+        <v>0.4088846181972901</v>
       </c>
       <c r="M19" t="n">
-        <v>4.081795412582079</v>
+        <v>4.081905003305923</v>
       </c>
       <c r="N19" t="n">
-        <v>25.87936651486837</v>
+        <v>25.84129074474563</v>
       </c>
       <c r="O19" t="n">
-        <v>5.087176674233791</v>
+        <v>5.08343296845209</v>
       </c>
       <c r="P19" t="n">
-        <v>347.1887561388639</v>
+        <v>347.2391429537468</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33639,28 +33851,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5972759160925892</v>
+        <v>0.5900198739493019</v>
       </c>
       <c r="J20" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K20" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3777373004272897</v>
+        <v>0.373758700072337</v>
       </c>
       <c r="M20" t="n">
-        <v>4.495444057613712</v>
+        <v>4.506092181515899</v>
       </c>
       <c r="N20" t="n">
-        <v>30.78460685619434</v>
+        <v>30.8481731872013</v>
       </c>
       <c r="O20" t="n">
-        <v>5.548387770892941</v>
+        <v>5.554113177384965</v>
       </c>
       <c r="P20" t="n">
-        <v>352.2014112868063</v>
+        <v>352.2763160812498</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33717,28 +33929,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.647618314870699</v>
+        <v>0.6339197327037234</v>
       </c>
       <c r="J21" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K21" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3757017799970229</v>
+        <v>0.3645998127181239</v>
       </c>
       <c r="M21" t="n">
-        <v>5.108578179321039</v>
+        <v>5.148634889112822</v>
       </c>
       <c r="N21" t="n">
-        <v>36.50789539621761</v>
+        <v>37.03780266046254</v>
       </c>
       <c r="O21" t="n">
-        <v>6.042176379105265</v>
+        <v>6.085869096559877</v>
       </c>
       <c r="P21" t="n">
-        <v>355.1388022192516</v>
+        <v>355.2802434236335</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33795,28 +34007,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5650431938342652</v>
+        <v>0.5466121863546192</v>
       </c>
       <c r="J22" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K22" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2239336686098347</v>
+        <v>0.211528513629291</v>
       </c>
       <c r="M22" t="n">
-        <v>6.507106381252894</v>
+        <v>6.565564584911272</v>
       </c>
       <c r="N22" t="n">
-        <v>57.96187855778443</v>
+        <v>58.90083736693389</v>
       </c>
       <c r="O22" t="n">
-        <v>7.613269899181589</v>
+        <v>7.674688095742646</v>
       </c>
       <c r="P22" t="n">
-        <v>352.3601632046033</v>
+        <v>352.5504793675022</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33873,28 +34085,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9913094325408143</v>
+        <v>0.9806406575918215</v>
       </c>
       <c r="J23" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K23" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5389888293138951</v>
+        <v>0.5345248283977351</v>
       </c>
       <c r="M23" t="n">
-        <v>5.391952043136734</v>
+        <v>5.410924174717786</v>
       </c>
       <c r="N23" t="n">
-        <v>44.03012015644725</v>
+        <v>44.2888295547135</v>
       </c>
       <c r="O23" t="n">
-        <v>6.635519584512373</v>
+        <v>6.654985315890149</v>
       </c>
       <c r="P23" t="n">
-        <v>342.8206711124621</v>
+        <v>342.9308110839174</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33951,28 +34163,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6826789956407437</v>
+        <v>0.6788887920147609</v>
       </c>
       <c r="J24" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K24" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4125935026582198</v>
+        <v>0.4132404483802395</v>
       </c>
       <c r="M24" t="n">
-        <v>4.912724784407515</v>
+        <v>4.898501545181817</v>
       </c>
       <c r="N24" t="n">
-        <v>34.75754967397084</v>
+        <v>34.60990412865308</v>
       </c>
       <c r="O24" t="n">
-        <v>5.895553381487681</v>
+        <v>5.883018283895868</v>
       </c>
       <c r="P24" t="n">
-        <v>354.2031275408338</v>
+        <v>354.2422491741315</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34029,28 +34241,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7251616292751006</v>
+        <v>0.713542667398355</v>
       </c>
       <c r="J25" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K25" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4569324388704864</v>
+        <v>0.4495111280083828</v>
       </c>
       <c r="M25" t="n">
-        <v>4.769206051291</v>
+        <v>4.784175360671691</v>
       </c>
       <c r="N25" t="n">
-        <v>32.73943740500646</v>
+        <v>32.9756804919938</v>
       </c>
       <c r="O25" t="n">
-        <v>5.721838638497809</v>
+        <v>5.742445514934713</v>
       </c>
       <c r="P25" t="n">
-        <v>361.4425601263524</v>
+        <v>361.5625618739979</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34107,28 +34319,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6162214896348502</v>
+        <v>0.6029532425371854</v>
       </c>
       <c r="J26" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K26" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4056554065574146</v>
+        <v>0.3944328860449169</v>
       </c>
       <c r="M26" t="n">
-        <v>4.297379811828608</v>
+        <v>4.335877187188462</v>
       </c>
       <c r="N26" t="n">
-        <v>29.14435416116193</v>
+        <v>29.51903865216595</v>
       </c>
       <c r="O26" t="n">
-        <v>5.398551116842549</v>
+        <v>5.433142612905163</v>
       </c>
       <c r="P26" t="n">
-        <v>347.0134485443756</v>
+        <v>347.1505033702735</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34185,28 +34397,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4209952109192232</v>
+        <v>0.4086042929008818</v>
       </c>
       <c r="J27" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K27" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2679011576534844</v>
+        <v>0.2557025369697099</v>
       </c>
       <c r="M27" t="n">
-        <v>3.893817794573786</v>
+        <v>3.936703121879065</v>
       </c>
       <c r="N27" t="n">
-        <v>25.37167559397117</v>
+        <v>25.70177555327905</v>
       </c>
       <c r="O27" t="n">
-        <v>5.037030434092211</v>
+        <v>5.069691859795726</v>
       </c>
       <c r="P27" t="n">
-        <v>344.9489128918466</v>
+        <v>345.0769006885324</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34263,28 +34475,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2533872083838487</v>
+        <v>0.2426401194862872</v>
       </c>
       <c r="J28" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K28" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1095663225472927</v>
+        <v>0.1016132070219097</v>
       </c>
       <c r="M28" t="n">
-        <v>4.056089276430469</v>
+        <v>4.081607592284155</v>
       </c>
       <c r="N28" t="n">
-        <v>27.33339481696735</v>
+        <v>27.52860456780695</v>
       </c>
       <c r="O28" t="n">
-        <v>5.228134927196059</v>
+        <v>5.246770870526647</v>
       </c>
       <c r="P28" t="n">
-        <v>360.6475041038944</v>
+        <v>360.7585100336061</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34341,28 +34553,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1247454460400091</v>
+        <v>0.1172071098929043</v>
       </c>
       <c r="J29" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K29" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L29" t="n">
-        <v>0.04052175641961853</v>
+        <v>0.03617643840832718</v>
       </c>
       <c r="M29" t="n">
-        <v>3.294791772111008</v>
+        <v>3.313179058393711</v>
       </c>
       <c r="N29" t="n">
-        <v>19.30171857733167</v>
+        <v>19.35643706405451</v>
       </c>
       <c r="O29" t="n">
-        <v>4.393372119150809</v>
+        <v>4.399595102285494</v>
       </c>
       <c r="P29" t="n">
-        <v>372.1121029650971</v>
+        <v>372.1899706367725</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34400,7 +34612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD298"/>
+  <dimension ref="A1:AD300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79307,6 +79519,310 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:06:07+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>-36.668201262235876,175.55783442916936</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>-36.66887451885718,175.55751415182593</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>-36.66956614960613,175.55725792803926</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-36.67018201687177,175.55673769269413</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-36.67082523627455,175.5563127986029</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-36.67148687549545,175.5560373297143</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-36.67216523798684,175.55583994044355</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-36.67287842184379,175.5557314982856</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-36.67357974893689,175.55544293776524</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-36.67429381567121,175.55531824350524</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-36.675008135511206,175.5551968885909</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-36.67572181796627,175.5550530769572</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-36.67644064744873,175.55497218222266</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-36.6771598946753,175.55492017196414</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-36.67788088732485,175.554871665794</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-36.678600222129205,175.55490298107566</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>-36.679324575129506,175.55492878997802</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>-36.680036261664924,175.55507027210317</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>-36.68074963149854,175.5551981922181</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>-36.68146386020645,175.5553191726924</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>-36.682183899411726,175.55545260616077</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>-36.68286097144704,175.55576691350893</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>-36.68352993891398,175.55611650632588</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>-36.68420189665573,175.55637767268868</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>-36.684861795826436,175.5567361948074</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>-36.68547143303824,175.5572258962455</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>-36.68597350196024,175.55788443040592</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>-36.68630191337294,175.55868109016453</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>-36.66823781029512,175.55796179688295</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>-36.668881562493596,175.55753869848465</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-36.66960829056798,175.5574047879249</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-36.67018497947568,175.55674801719914</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-36.67082647574195,175.55631711807092</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-36.67148812637863,175.55604385786665</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-36.67216938611873,175.55588640476716</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-36.672878967367254,175.55573851160236</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-36.67358164532395,175.5554673176101</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-36.67429486345366,175.55533171377243</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-36.67500759862729,175.55518998640667</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-36.67572101838784,175.55504081417942</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-36.676440993894246,175.55497887915462</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-36.677159883332,175.5549199487148</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-36.677881068452535,175.55488161768818</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-36.67859903788851,175.5549232843607</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-36.679318444811805,175.55498870735087</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>-36.68002955229484,175.5551358489264</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>-36.680739338766806,175.55528370403215</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>-36.68144378366255,175.55542855690118</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>-36.68215496450174,175.55557868036232</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>-36.68283490016075,175.55588051027027</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>-36.683518038837285,175.5561683567672</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>-36.68418818305838,175.55641205443368</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>-36.6848564453992,175.556744773592</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>-36.6854623742782,175.55723996129407</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>-36.68596179826311,175.5578978779434</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>-36.68629810879069,175.55868428862723</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD300"/>
+  <dimension ref="A1:AD301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29008,7 +29008,7 @@
         <v>407.05</v>
       </c>
       <c r="D300" t="n">
-        <v>424.38</v>
+        <v>412.66</v>
       </c>
       <c r="E300" t="n">
         <v>392.08</v>
@@ -29086,6 +29086,102 @@
         <v>370.35</v>
       </c>
       <c r="AD300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>417.17</v>
+      </c>
+      <c r="C301" t="n">
+        <v>407.05</v>
+      </c>
+      <c r="D301" t="n">
+        <v>400.35</v>
+      </c>
+      <c r="E301" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="F301" t="n">
+        <v>381</v>
+      </c>
+      <c r="G301" t="n">
+        <v>384.02</v>
+      </c>
+      <c r="H301" t="n">
+        <v>378.09</v>
+      </c>
+      <c r="I301" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="J301" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="K301" t="n">
+        <v>355.89</v>
+      </c>
+      <c r="L301" t="n">
+        <v>354.44</v>
+      </c>
+      <c r="M301" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="N301" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="O301" t="n">
+        <v>352.15</v>
+      </c>
+      <c r="P301" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="R301" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="S301" t="n">
+        <v>362.46</v>
+      </c>
+      <c r="T301" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="U301" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="V301" t="n">
+        <v>366.64</v>
+      </c>
+      <c r="W301" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="X301" t="n">
+        <v>372.13</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>362.65</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="AD301" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29102,7 +29198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B317"/>
+  <dimension ref="A1:B318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32275,6 +32371,16 @@
       </c>
       <c r="B317" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -32443,28 +32549,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.022793875439326</v>
+        <v>-6.990610968033517</v>
       </c>
       <c r="J2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K2" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7735439478474904</v>
+        <v>0.7719164185720409</v>
       </c>
       <c r="M2" t="n">
-        <v>19.51018005686012</v>
+        <v>19.57132257616195</v>
       </c>
       <c r="N2" t="n">
-        <v>697.4049080246582</v>
+        <v>700.7982059705905</v>
       </c>
       <c r="O2" t="n">
-        <v>26.40842494403364</v>
+        <v>26.47259348780528</v>
       </c>
       <c r="P2" t="n">
-        <v>561.6347978551671</v>
+        <v>561.2743102725478</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32525,28 +32631,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.732583622547929</v>
+        <v>-3.718927565958978</v>
       </c>
       <c r="J3" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4815919871436227</v>
+        <v>0.4814870892543255</v>
       </c>
       <c r="M3" t="n">
-        <v>22.54780163575558</v>
+        <v>22.5275533884592</v>
       </c>
       <c r="N3" t="n">
-        <v>791.400381401898</v>
+        <v>789.7466960423423</v>
       </c>
       <c r="O3" t="n">
-        <v>28.13183928224207</v>
+        <v>28.1024322086602</v>
       </c>
       <c r="P3" t="n">
-        <v>487.1753703347477</v>
+        <v>487.032533745892</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32603,28 +32709,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.264800482680998</v>
+        <v>2.242472033260017</v>
       </c>
       <c r="J4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1782416180759679</v>
+        <v>0.1764352456260347</v>
       </c>
       <c r="M4" t="n">
-        <v>29.46191020883406</v>
+        <v>29.4309967579986</v>
       </c>
       <c r="N4" t="n">
-        <v>1259.446674704517</v>
+        <v>1255.912992592559</v>
       </c>
       <c r="O4" t="n">
-        <v>35.48868375559337</v>
+        <v>35.43886274406332</v>
       </c>
       <c r="P4" t="n">
-        <v>358.5821672783029</v>
+        <v>358.8168379044034</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32681,28 +32787,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.796050157251418</v>
+        <v>1.786652468604659</v>
       </c>
       <c r="J5" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K5" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5656621418715462</v>
+        <v>0.5640245938394475</v>
       </c>
       <c r="M5" t="n">
-        <v>8.961787120022674</v>
+        <v>8.970225593211127</v>
       </c>
       <c r="N5" t="n">
-        <v>127.6030696068365</v>
+        <v>127.7263505186438</v>
       </c>
       <c r="O5" t="n">
-        <v>11.29615286754019</v>
+        <v>11.30160831557367</v>
       </c>
       <c r="P5" t="n">
-        <v>352.4452528491931</v>
+        <v>352.5445007925622</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32759,28 +32865,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7100011151433874</v>
+        <v>0.7088761807988484</v>
       </c>
       <c r="J6" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K6" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4033624286200765</v>
+        <v>0.4045166792272862</v>
       </c>
       <c r="M6" t="n">
-        <v>3.209514904443327</v>
+        <v>3.203205535620834</v>
       </c>
       <c r="N6" t="n">
-        <v>38.16612783104744</v>
+        <v>38.04555259807501</v>
       </c>
       <c r="O6" t="n">
-        <v>6.177874054320583</v>
+        <v>6.168107699941288</v>
       </c>
       <c r="P6" t="n">
-        <v>363.8337057555415</v>
+        <v>363.8456263992393</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32837,28 +32943,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2454885254057575</v>
+        <v>0.2460143211826435</v>
       </c>
       <c r="J7" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02896501176789579</v>
+        <v>0.02931422649087356</v>
       </c>
       <c r="M7" t="n">
-        <v>4.261636056657993</v>
+        <v>4.248706887662927</v>
       </c>
       <c r="N7" t="n">
-        <v>105.2276377798047</v>
+        <v>104.8751188150201</v>
       </c>
       <c r="O7" t="n">
-        <v>10.25805233851947</v>
+        <v>10.24085537516374</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8197535293706</v>
+        <v>376.814234542168</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32915,28 +33021,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03866732985868792</v>
+        <v>0.04159530307133769</v>
       </c>
       <c r="J8" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K8" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009078079330687716</v>
+        <v>0.001058159053551</v>
       </c>
       <c r="M8" t="n">
-        <v>6.089922943584225</v>
+        <v>6.080112542063443</v>
       </c>
       <c r="N8" t="n">
-        <v>86.17634506863529</v>
+        <v>85.94285295271793</v>
       </c>
       <c r="O8" t="n">
-        <v>9.283121515343602</v>
+        <v>9.270536821172652</v>
       </c>
       <c r="P8" t="n">
-        <v>372.9700244696094</v>
+        <v>372.9394335820315</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32993,28 +33099,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01438480338247265</v>
+        <v>-0.01293146890430917</v>
       </c>
       <c r="J9" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K9" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L9" t="n">
-        <v>8.232696696175434e-05</v>
+        <v>6.70660552272162e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.91515003568054</v>
+        <v>7.89487103898825</v>
       </c>
       <c r="N9" t="n">
-        <v>132.4669248608263</v>
+        <v>132.0331795061824</v>
       </c>
       <c r="O9" t="n">
-        <v>11.50942765131378</v>
+        <v>11.49056915501501</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2459316059758</v>
+        <v>370.2308003054563</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33071,28 +33177,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3535434814156669</v>
+        <v>-0.351703789394979</v>
       </c>
       <c r="J10" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K10" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04613512732844505</v>
+        <v>0.04602673038953076</v>
       </c>
       <c r="M10" t="n">
-        <v>8.303936917745203</v>
+        <v>8.284672915817584</v>
       </c>
       <c r="N10" t="n">
-        <v>133.7283819311802</v>
+        <v>133.3011856135749</v>
       </c>
       <c r="O10" t="n">
-        <v>11.56409883783342</v>
+        <v>11.54561326277538</v>
       </c>
       <c r="P10" t="n">
-        <v>365.970402080903</v>
+        <v>365.9510535810902</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33149,28 +33255,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01772327595144314</v>
+        <v>-0.01680834007232468</v>
       </c>
       <c r="J11" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K11" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001851970467747766</v>
+        <v>0.0001679266692922177</v>
       </c>
       <c r="M11" t="n">
-        <v>6.221245773221479</v>
+        <v>6.205525823756211</v>
       </c>
       <c r="N11" t="n">
-        <v>86.83142807012733</v>
+        <v>86.54333660805629</v>
       </c>
       <c r="O11" t="n">
-        <v>9.31833826763803</v>
+        <v>9.302867117617895</v>
       </c>
       <c r="P11" t="n">
-        <v>355.1002320017382</v>
+        <v>355.0905232298882</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33227,28 +33333,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1281711134962176</v>
+        <v>0.1279978440889069</v>
       </c>
       <c r="J12" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K12" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02605831928872959</v>
+        <v>0.02619398571730314</v>
       </c>
       <c r="M12" t="n">
-        <v>4.353975565953416</v>
+        <v>4.340237743758992</v>
       </c>
       <c r="N12" t="n">
-        <v>32.47226932831133</v>
+        <v>32.364225958403</v>
       </c>
       <c r="O12" t="n">
-        <v>5.698444465668795</v>
+        <v>5.688956491168042</v>
       </c>
       <c r="P12" t="n">
-        <v>351.3036293720355</v>
+        <v>351.3054239712468</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33305,28 +33411,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.222256943515189</v>
+        <v>0.2189891515263082</v>
       </c>
       <c r="J13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1148145588560114</v>
+        <v>0.112290753781483</v>
       </c>
       <c r="M13" t="n">
-        <v>3.422140291423021</v>
+        <v>3.424157040834621</v>
       </c>
       <c r="N13" t="n">
-        <v>20.14158997802371</v>
+        <v>20.1447089545043</v>
       </c>
       <c r="O13" t="n">
-        <v>4.487938276984623</v>
+        <v>4.488285747866806</v>
       </c>
       <c r="P13" t="n">
-        <v>348.28293840895</v>
+        <v>348.3167838350815</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33383,28 +33489,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1548224320692007</v>
+        <v>0.1535778293065282</v>
       </c>
       <c r="J14" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K14" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05684776081940568</v>
+        <v>0.05638920611881892</v>
       </c>
       <c r="M14" t="n">
-        <v>3.635642835081201</v>
+        <v>3.629742067452395</v>
       </c>
       <c r="N14" t="n">
-        <v>21.03206826641504</v>
+        <v>20.97215305935324</v>
       </c>
       <c r="O14" t="n">
-        <v>4.586073294923996</v>
+        <v>4.579536336721572</v>
       </c>
       <c r="P14" t="n">
-        <v>349.0431246154865</v>
+        <v>349.0560153107972</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33461,28 +33567,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2917641048031678</v>
+        <v>0.2883567001443552</v>
       </c>
       <c r="J15" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K15" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1939623524318667</v>
+        <v>0.1909258076148619</v>
       </c>
       <c r="M15" t="n">
-        <v>3.397796104931616</v>
+        <v>3.40178385589889</v>
       </c>
       <c r="N15" t="n">
-        <v>18.70886234642364</v>
+        <v>18.7228886766534</v>
       </c>
       <c r="O15" t="n">
-        <v>4.325374243510455</v>
+        <v>4.326995340493609</v>
       </c>
       <c r="P15" t="n">
-        <v>349.2767536665127</v>
+        <v>349.3120450997107</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33539,28 +33645,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3549660831623034</v>
+        <v>0.3517791140686264</v>
       </c>
       <c r="J16" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K16" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2506778793365679</v>
+        <v>0.2481778020385186</v>
       </c>
       <c r="M16" t="n">
-        <v>3.247720586592378</v>
+        <v>3.253507210597535</v>
       </c>
       <c r="N16" t="n">
-        <v>19.91920645891008</v>
+        <v>19.91963430394811</v>
       </c>
       <c r="O16" t="n">
-        <v>4.463093821432626</v>
+        <v>4.463141752616435</v>
       </c>
       <c r="P16" t="n">
-        <v>351.4249770695727</v>
+        <v>351.4579853906075</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33617,28 +33723,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4641925211244187</v>
+        <v>0.4618370806005749</v>
       </c>
       <c r="J17" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K17" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3655004860160029</v>
+        <v>0.364577903064265</v>
       </c>
       <c r="M17" t="n">
-        <v>3.350483308233973</v>
+        <v>3.350501224538601</v>
       </c>
       <c r="N17" t="n">
-        <v>19.78269191921518</v>
+        <v>19.75325263715701</v>
       </c>
       <c r="O17" t="n">
-        <v>4.44777381610342</v>
+        <v>4.444463143863048</v>
       </c>
       <c r="P17" t="n">
-        <v>350.8895589656728</v>
+        <v>350.9139549151482</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33695,28 +33801,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5589039984501559</v>
+        <v>0.5569395433876599</v>
       </c>
       <c r="J18" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K18" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4412484380732926</v>
+        <v>0.4411953419761288</v>
       </c>
       <c r="M18" t="n">
-        <v>3.609512299797915</v>
+        <v>3.608047458296629</v>
       </c>
       <c r="N18" t="n">
-        <v>20.91971564327567</v>
+        <v>20.87537361204526</v>
       </c>
       <c r="O18" t="n">
-        <v>4.573807565177581</v>
+        <v>4.568957606724455</v>
       </c>
       <c r="P18" t="n">
-        <v>346.3440589210293</v>
+        <v>346.3644053258595</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33773,28 +33879,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5813644482648999</v>
+        <v>0.5812954016174849</v>
       </c>
       <c r="J19" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K19" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4088846181972901</v>
+        <v>0.4107723916592375</v>
       </c>
       <c r="M19" t="n">
-        <v>4.081905003305923</v>
+        <v>4.06868258318515</v>
       </c>
       <c r="N19" t="n">
-        <v>25.84129074474563</v>
+        <v>25.75518447569662</v>
       </c>
       <c r="O19" t="n">
-        <v>5.08343296845209</v>
+        <v>5.074956598405215</v>
       </c>
       <c r="P19" t="n">
-        <v>347.2391429537468</v>
+        <v>347.2398580889857</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33851,28 +33957,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5900198739493019</v>
+        <v>0.5916775527046528</v>
       </c>
       <c r="J20" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K20" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L20" t="n">
-        <v>0.373758700072337</v>
+        <v>0.3768222201971237</v>
       </c>
       <c r="M20" t="n">
-        <v>4.506092181515899</v>
+        <v>4.497296053175748</v>
       </c>
       <c r="N20" t="n">
-        <v>30.8481731872013</v>
+        <v>30.76342539705893</v>
       </c>
       <c r="O20" t="n">
-        <v>5.554113177384965</v>
+        <v>5.546478648391152</v>
       </c>
       <c r="P20" t="n">
-        <v>352.2763160812498</v>
+        <v>352.2591470435462</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33929,28 +34035,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6339197327037234</v>
+        <v>0.6344516419375621</v>
       </c>
       <c r="J21" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K21" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3645998127181239</v>
+        <v>0.3668431229947617</v>
       </c>
       <c r="M21" t="n">
-        <v>5.148634889112822</v>
+        <v>5.133571659327481</v>
       </c>
       <c r="N21" t="n">
-        <v>37.03780266046254</v>
+        <v>36.91620480360921</v>
       </c>
       <c r="O21" t="n">
-        <v>6.085869096559877</v>
+        <v>6.075870703332092</v>
       </c>
       <c r="P21" t="n">
-        <v>355.2802434236335</v>
+        <v>355.2747342924698</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34007,28 +34113,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5466121863546192</v>
+        <v>0.5463922868851337</v>
       </c>
       <c r="J22" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K22" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L22" t="n">
-        <v>0.211528513629291</v>
+        <v>0.2127374716845649</v>
       </c>
       <c r="M22" t="n">
-        <v>6.565564584911272</v>
+        <v>6.544884804977065</v>
       </c>
       <c r="N22" t="n">
-        <v>58.90083736693389</v>
+        <v>58.70481939310894</v>
       </c>
       <c r="O22" t="n">
-        <v>7.674688095742646</v>
+        <v>7.661907033703094</v>
       </c>
       <c r="P22" t="n">
-        <v>352.5504793675022</v>
+        <v>352.5527569271743</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34085,28 +34191,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9806406575918215</v>
+        <v>0.9803010923664613</v>
       </c>
       <c r="J23" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K23" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5345248283977351</v>
+        <v>0.5363490842782611</v>
       </c>
       <c r="M23" t="n">
-        <v>5.410924174717786</v>
+        <v>5.394622477727151</v>
       </c>
       <c r="N23" t="n">
-        <v>44.2888295547135</v>
+        <v>44.14195875455214</v>
       </c>
       <c r="O23" t="n">
-        <v>6.654985315890149</v>
+        <v>6.643941507460172</v>
       </c>
       <c r="P23" t="n">
-        <v>342.9308110839174</v>
+        <v>342.9343280549459</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34163,28 +34269,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6788887920147609</v>
+        <v>0.6788899657821136</v>
       </c>
       <c r="J24" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K24" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4132404483802395</v>
+        <v>0.4151930212596585</v>
       </c>
       <c r="M24" t="n">
-        <v>4.898501545181817</v>
+        <v>4.882178425685111</v>
       </c>
       <c r="N24" t="n">
-        <v>34.60990412865308</v>
+        <v>34.49453779062218</v>
       </c>
       <c r="O24" t="n">
-        <v>5.883018283895868</v>
+        <v>5.873205069689137</v>
       </c>
       <c r="P24" t="n">
-        <v>354.2422491741315</v>
+        <v>354.2422370170981</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34241,28 +34347,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.713542667398355</v>
+        <v>0.7094747381026312</v>
       </c>
       <c r="J25" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K25" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4495111280083828</v>
+        <v>0.447854208755191</v>
       </c>
       <c r="M25" t="n">
-        <v>4.784175360671691</v>
+        <v>4.784478785459598</v>
       </c>
       <c r="N25" t="n">
-        <v>32.9756804919938</v>
+        <v>32.9746373559047</v>
       </c>
       <c r="O25" t="n">
-        <v>5.742445514934713</v>
+        <v>5.742354687399995</v>
       </c>
       <c r="P25" t="n">
-        <v>361.5625618739979</v>
+        <v>361.6046945436892</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34319,28 +34425,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6029532425371854</v>
+        <v>0.5981350972658771</v>
       </c>
       <c r="J26" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K26" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3944328860449169</v>
+        <v>0.3912891018839498</v>
       </c>
       <c r="M26" t="n">
-        <v>4.335877187188462</v>
+        <v>4.345630737559962</v>
       </c>
       <c r="N26" t="n">
-        <v>29.51903865216595</v>
+        <v>29.5733788873441</v>
       </c>
       <c r="O26" t="n">
-        <v>5.433142612905163</v>
+        <v>5.438141124257819</v>
       </c>
       <c r="P26" t="n">
-        <v>347.1505033702735</v>
+        <v>347.2004062344785</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34397,28 +34503,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4086042929008818</v>
+        <v>0.4048580366054518</v>
       </c>
       <c r="J27" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K27" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2557025369697099</v>
+        <v>0.2530517544076287</v>
       </c>
       <c r="M27" t="n">
-        <v>3.936703121879065</v>
+        <v>3.94439240118686</v>
       </c>
       <c r="N27" t="n">
-        <v>25.70177555327905</v>
+        <v>25.70844077053164</v>
       </c>
       <c r="O27" t="n">
-        <v>5.069691859795726</v>
+        <v>5.070349176391271</v>
       </c>
       <c r="P27" t="n">
-        <v>345.0769006885324</v>
+        <v>345.1157017019227</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34475,28 +34581,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2426401194862872</v>
+        <v>0.2394539659859856</v>
       </c>
       <c r="J28" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K28" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1016132070219097</v>
+        <v>0.099727933545249</v>
       </c>
       <c r="M28" t="n">
-        <v>4.081607592284155</v>
+        <v>4.083610658413964</v>
       </c>
       <c r="N28" t="n">
-        <v>27.52860456780695</v>
+        <v>27.50363355370894</v>
       </c>
       <c r="O28" t="n">
-        <v>5.246770870526647</v>
+        <v>5.244390675160361</v>
       </c>
       <c r="P28" t="n">
-        <v>360.7585100336061</v>
+        <v>360.7915099073145</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34553,28 +34659,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1172071098929043</v>
+        <v>0.1146010104730588</v>
       </c>
       <c r="J29" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K29" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L29" t="n">
-        <v>0.03617643840832718</v>
+        <v>0.03483279793088967</v>
       </c>
       <c r="M29" t="n">
-        <v>3.313179058393711</v>
+        <v>3.316387307130829</v>
       </c>
       <c r="N29" t="n">
-        <v>19.35643706405451</v>
+        <v>19.33660109691312</v>
       </c>
       <c r="O29" t="n">
-        <v>4.399595102285494</v>
+        <v>4.397340229833612</v>
       </c>
       <c r="P29" t="n">
-        <v>372.1899706367725</v>
+        <v>372.2169627298147</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34612,7 +34718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD300"/>
+  <dimension ref="A1:AD301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79689,7 +79795,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-36.66960829056798,175.5574047879249</t>
+          <t>-36.66957286073315,175.55728131604536</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -79818,6 +79924,158 @@
         </is>
       </c>
       <c r="AD300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>-36.66823781029512,175.55796179688295</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>-36.668881562493596,175.55753869848465</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-36.66953564717153,175.55715162854614</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-36.67016928975661,175.55669333947176</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-36.67082581066191,175.55631480030758</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-36.67148677125516,175.55603678570156</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-36.67216596242268,175.5558480550261</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-36.672874204846714,175.55567728423645</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-36.673579047532186,175.55543392056256</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-36.67429201452092,175.55529508800524</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-36.675006585474286,175.5551769613173</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-36.675719651832665,175.5550198559778</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-36.67644031832513,175.55496582013737</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-36.67715899288158,175.5549024236416</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-36.67788096059008,175.55487569127928</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-36.67859953891385,175.55491469450948</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-36.67931775231108,175.55499547579413</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>-36.68002916630631,175.5551396215351</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>-36.68073467838969,175.5553224221799</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>-36.681433375046694,175.55548526653612</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>-36.68213884286147,175.55564892473242</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>-36.682830851201516,175.55589815218414</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>-36.68351744630177,175.55617093853144</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>-36.68418590412145,175.5564177680169</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>-36.684846185815424,175.55676122362914</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>-36.68544864547125,175.55726127726192</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>-36.68594850762231,175.55791314887088</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>-36.68628878383387,175.55869212799522</t>
+        </is>
+      </c>
+      <c r="AD301" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD301"/>
+  <dimension ref="A1:AD302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29182,6 +29182,102 @@
         <v>371.6</v>
       </c>
       <c r="AD301" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>417.17</v>
+      </c>
+      <c r="C302" t="n">
+        <v>394.64</v>
+      </c>
+      <c r="D302" t="n">
+        <v>391.27</v>
+      </c>
+      <c r="E302" t="n">
+        <v>382.87</v>
+      </c>
+      <c r="F302" t="n">
+        <v>380.75</v>
+      </c>
+      <c r="G302" t="n">
+        <v>382.62</v>
+      </c>
+      <c r="H302" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="I302" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="J302" t="n">
+        <v>356.35</v>
+      </c>
+      <c r="K302" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="L302" t="n">
+        <v>353.3</v>
+      </c>
+      <c r="M302" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="N302" t="n">
+        <v>350.23</v>
+      </c>
+      <c r="O302" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="P302" t="n">
+        <v>356.15</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>359.44</v>
+      </c>
+      <c r="R302" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="S302" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="T302" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="U302" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="V302" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="W302" t="n">
+        <v>368.31</v>
+      </c>
+      <c r="X302" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>364.94</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="AD302" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29198,7 +29294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B318"/>
+  <dimension ref="A1:B319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32381,6 +32477,16 @@
       </c>
       <c r="B318" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -32549,28 +32655,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.990610968033517</v>
+        <v>-6.958822798589178</v>
       </c>
       <c r="J2" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7719164185720409</v>
+        <v>0.7703080828051827</v>
       </c>
       <c r="M2" t="n">
-        <v>19.57132257616195</v>
+        <v>19.63552216488234</v>
       </c>
       <c r="N2" t="n">
-        <v>700.7982059705905</v>
+        <v>704.1145265240098</v>
       </c>
       <c r="O2" t="n">
-        <v>26.47259348780528</v>
+        <v>26.53515642546714</v>
       </c>
       <c r="P2" t="n">
-        <v>561.2743102725478</v>
+        <v>560.9176390524211</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32631,28 +32737,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.718927565958978</v>
+        <v>-3.714647923277984</v>
       </c>
       <c r="J3" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K3" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4814870892543255</v>
+        <v>0.4829556110127347</v>
       </c>
       <c r="M3" t="n">
-        <v>22.5275533884592</v>
+        <v>22.46612977969165</v>
       </c>
       <c r="N3" t="n">
-        <v>789.7466960423423</v>
+        <v>787.0528294784174</v>
       </c>
       <c r="O3" t="n">
-        <v>28.1024322086602</v>
+        <v>28.05446184617373</v>
       </c>
       <c r="P3" t="n">
-        <v>487.032533745892</v>
+        <v>486.9876904420155</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32709,28 +32815,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.242472033260017</v>
+        <v>2.222461623938193</v>
       </c>
       <c r="J4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K4" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1764352456260347</v>
+        <v>0.1747355683356572</v>
       </c>
       <c r="M4" t="n">
-        <v>29.4309967579986</v>
+        <v>29.43433493563135</v>
       </c>
       <c r="N4" t="n">
-        <v>1255.912992592559</v>
+        <v>1253.891389760144</v>
       </c>
       <c r="O4" t="n">
-        <v>35.43886274406332</v>
+        <v>35.41032885698951</v>
       </c>
       <c r="P4" t="n">
-        <v>358.8168379044034</v>
+        <v>359.0276915866715</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32787,28 +32893,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.786652468604659</v>
+        <v>1.774464384352385</v>
       </c>
       <c r="J5" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K5" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5640245938394475</v>
+        <v>0.5608347290294602</v>
       </c>
       <c r="M5" t="n">
-        <v>8.970225593211127</v>
+        <v>8.990377053222367</v>
       </c>
       <c r="N5" t="n">
-        <v>127.7263505186438</v>
+        <v>128.2409272020867</v>
       </c>
       <c r="O5" t="n">
-        <v>11.30160831557367</v>
+        <v>11.32435107200791</v>
       </c>
       <c r="P5" t="n">
-        <v>352.5445007925622</v>
+        <v>352.6734395299455</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32865,28 +32971,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7088761807988484</v>
+        <v>0.7075694808800551</v>
       </c>
       <c r="J6" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K6" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4045166792272862</v>
+        <v>0.4055145572751689</v>
       </c>
       <c r="M6" t="n">
-        <v>3.203205535620834</v>
+        <v>3.197647722047766</v>
       </c>
       <c r="N6" t="n">
-        <v>38.04555259807501</v>
+        <v>37.92871006648505</v>
       </c>
       <c r="O6" t="n">
-        <v>6.168107699941288</v>
+        <v>6.158628911250056</v>
       </c>
       <c r="P6" t="n">
-        <v>363.8456263992393</v>
+        <v>363.859496829086</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32943,28 +33049,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2460143211826435</v>
+        <v>0.2455266129812995</v>
       </c>
       <c r="J7" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K7" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02931422649087356</v>
+        <v>0.02942946743658503</v>
       </c>
       <c r="M7" t="n">
-        <v>4.248706887662927</v>
+        <v>4.237685491972638</v>
       </c>
       <c r="N7" t="n">
-        <v>104.8751188150201</v>
+        <v>104.5247407697453</v>
       </c>
       <c r="O7" t="n">
-        <v>10.24085537516374</v>
+        <v>10.22373418911824</v>
       </c>
       <c r="P7" t="n">
-        <v>376.814234542168</v>
+        <v>376.8193626769083</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33021,28 +33127,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04159530307133769</v>
+        <v>0.04316132207461834</v>
       </c>
       <c r="J8" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K8" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001058159053551</v>
+        <v>0.001148181028473472</v>
       </c>
       <c r="M8" t="n">
-        <v>6.080112542063443</v>
+        <v>6.065689288413964</v>
       </c>
       <c r="N8" t="n">
-        <v>85.94285295271793</v>
+        <v>85.67153598559906</v>
       </c>
       <c r="O8" t="n">
-        <v>9.270536821172652</v>
+        <v>9.255891960562151</v>
       </c>
       <c r="P8" t="n">
-        <v>372.9394335820315</v>
+        <v>372.923043489156</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33099,28 +33205,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01293146890430917</v>
+        <v>-0.01411121956200222</v>
       </c>
       <c r="J9" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L9" t="n">
-        <v>6.70660552272162e-05</v>
+        <v>8.049833821188734e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.89487103898825</v>
+        <v>7.874145899495981</v>
       </c>
       <c r="N9" t="n">
-        <v>132.0331795061824</v>
+        <v>131.5978091915793</v>
       </c>
       <c r="O9" t="n">
-        <v>11.49056915501501</v>
+        <v>11.47160883187617</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2308003054563</v>
+        <v>370.2431048749712</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33177,28 +33283,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.351703789394979</v>
+        <v>-0.3519295948721602</v>
       </c>
       <c r="J10" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K10" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04602673038953076</v>
+        <v>0.0464392247700236</v>
       </c>
       <c r="M10" t="n">
-        <v>8.284672915817584</v>
+        <v>8.258002054460391</v>
       </c>
       <c r="N10" t="n">
-        <v>133.3011856135749</v>
+        <v>132.8556908451187</v>
       </c>
       <c r="O10" t="n">
-        <v>11.54561326277538</v>
+        <v>11.52630430125453</v>
       </c>
       <c r="P10" t="n">
-        <v>365.9510535810902</v>
+        <v>365.9534325307212</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33255,28 +33361,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01680834007232468</v>
+        <v>-0.01732112991512446</v>
       </c>
       <c r="J11" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K11" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001679266692922177</v>
+        <v>0.0001797740458919783</v>
       </c>
       <c r="M11" t="n">
-        <v>6.205525823756211</v>
+        <v>6.186401473864565</v>
       </c>
       <c r="N11" t="n">
-        <v>86.54333660805629</v>
+        <v>86.25361609090753</v>
       </c>
       <c r="O11" t="n">
-        <v>9.302867117617895</v>
+        <v>9.287282492252915</v>
       </c>
       <c r="P11" t="n">
-        <v>355.0905232298882</v>
+        <v>355.0959739954792</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33333,28 +33439,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1279978440889069</v>
+        <v>0.1270270019649651</v>
       </c>
       <c r="J12" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K12" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02619398571730314</v>
+        <v>0.02600503142463761</v>
       </c>
       <c r="M12" t="n">
-        <v>4.340237743758992</v>
+        <v>4.330133901997576</v>
       </c>
       <c r="N12" t="n">
-        <v>32.364225958403</v>
+        <v>32.26297737998765</v>
       </c>
       <c r="O12" t="n">
-        <v>5.688956491168042</v>
+        <v>5.680050825475741</v>
       </c>
       <c r="P12" t="n">
-        <v>351.3054239712468</v>
+        <v>351.3154969371713</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33411,28 +33517,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2189891515263082</v>
+        <v>0.2156149183378585</v>
       </c>
       <c r="J13" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K13" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L13" t="n">
-        <v>0.112290753781483</v>
+        <v>0.1096434402814651</v>
       </c>
       <c r="M13" t="n">
-        <v>3.424157040834621</v>
+        <v>3.426735255167354</v>
       </c>
       <c r="N13" t="n">
-        <v>20.1447089545043</v>
+        <v>20.1535676778362</v>
       </c>
       <c r="O13" t="n">
-        <v>4.488285747866806</v>
+        <v>4.489272510979502</v>
       </c>
       <c r="P13" t="n">
-        <v>348.3167838350815</v>
+        <v>348.3517931688241</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33489,28 +33595,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1535778293065282</v>
+        <v>0.15155859069213</v>
       </c>
       <c r="J14" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K14" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05638920611881892</v>
+        <v>0.05534592321426657</v>
       </c>
       <c r="M14" t="n">
-        <v>3.629742067452395</v>
+        <v>3.627704495369361</v>
       </c>
       <c r="N14" t="n">
-        <v>20.97215305935324</v>
+        <v>20.92961791987457</v>
       </c>
       <c r="O14" t="n">
-        <v>4.579536336721572</v>
+        <v>4.574889935274352</v>
       </c>
       <c r="P14" t="n">
-        <v>349.0560153107972</v>
+        <v>349.0769659074541</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33567,28 +33673,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2883567001443552</v>
+        <v>0.284391383819714</v>
       </c>
       <c r="J15" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K15" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1909258076148619</v>
+        <v>0.1870483855586981</v>
       </c>
       <c r="M15" t="n">
-        <v>3.40178385589889</v>
+        <v>3.409069547594184</v>
       </c>
       <c r="N15" t="n">
-        <v>18.7228886766534</v>
+        <v>18.76534785991585</v>
       </c>
       <c r="O15" t="n">
-        <v>4.326995340493609</v>
+        <v>4.331898874617902</v>
       </c>
       <c r="P15" t="n">
-        <v>349.3120450997107</v>
+        <v>349.3531872125556</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33645,28 +33751,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3517791140686264</v>
+        <v>0.3485543406968052</v>
       </c>
       <c r="J16" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K16" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2481778020385186</v>
+        <v>0.2455913215169516</v>
       </c>
       <c r="M16" t="n">
-        <v>3.253507210597535</v>
+        <v>3.259515331873983</v>
       </c>
       <c r="N16" t="n">
-        <v>19.91963430394811</v>
+        <v>19.92267579214727</v>
       </c>
       <c r="O16" t="n">
-        <v>4.463141752616435</v>
+        <v>4.463482473601444</v>
       </c>
       <c r="P16" t="n">
-        <v>351.4579853906075</v>
+        <v>351.4914440050284</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33723,28 +33829,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4618370806005749</v>
+        <v>0.4592623153922726</v>
       </c>
       <c r="J17" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K17" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L17" t="n">
-        <v>0.364577903064265</v>
+        <v>0.3633204470205976</v>
       </c>
       <c r="M17" t="n">
-        <v>3.350501224538601</v>
+        <v>3.351513522714553</v>
       </c>
       <c r="N17" t="n">
-        <v>19.75325263715701</v>
+        <v>19.7317544184451</v>
       </c>
       <c r="O17" t="n">
-        <v>4.444463143863048</v>
+        <v>4.442043946028123</v>
       </c>
       <c r="P17" t="n">
-        <v>350.9139549151482</v>
+        <v>350.9406693742422</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33801,28 +33907,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5569395433876599</v>
+        <v>0.5552847120253033</v>
       </c>
       <c r="J18" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K18" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4411953419761288</v>
+        <v>0.4414815979130997</v>
       </c>
       <c r="M18" t="n">
-        <v>3.608047458296629</v>
+        <v>3.604902162038522</v>
       </c>
       <c r="N18" t="n">
-        <v>20.87537361204526</v>
+        <v>20.8242481956268</v>
       </c>
       <c r="O18" t="n">
-        <v>4.568957606724455</v>
+        <v>4.563359310379449</v>
       </c>
       <c r="P18" t="n">
-        <v>346.3644053258595</v>
+        <v>346.3815750175248</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33879,28 +33985,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5812954016174849</v>
+        <v>0.5809161107457349</v>
       </c>
       <c r="J19" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K19" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4107723916592375</v>
+        <v>0.4123817903931483</v>
       </c>
       <c r="M19" t="n">
-        <v>4.06868258318515</v>
+        <v>4.057260221688009</v>
       </c>
       <c r="N19" t="n">
-        <v>25.75518447569662</v>
+        <v>25.67057666069502</v>
       </c>
       <c r="O19" t="n">
-        <v>5.074956598405215</v>
+        <v>5.066613924574776</v>
       </c>
       <c r="P19" t="n">
-        <v>347.2398580889857</v>
+        <v>347.2437934188735</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33957,28 +34063,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5916775527046528</v>
+        <v>0.5932629301157878</v>
       </c>
       <c r="J20" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K20" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3768222201971237</v>
+        <v>0.3798313981010938</v>
       </c>
       <c r="M20" t="n">
-        <v>4.497296053175748</v>
+        <v>4.488259590520625</v>
       </c>
       <c r="N20" t="n">
-        <v>30.76342539705893</v>
+        <v>30.67795134717415</v>
       </c>
       <c r="O20" t="n">
-        <v>5.546478648391152</v>
+        <v>5.538768035147722</v>
       </c>
       <c r="P20" t="n">
-        <v>352.2591470435462</v>
+        <v>352.2426979708846</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34035,28 +34141,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6344516419375621</v>
+        <v>0.6359579753804582</v>
       </c>
       <c r="J21" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K21" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3668431229947617</v>
+        <v>0.3697094793684285</v>
       </c>
       <c r="M21" t="n">
-        <v>5.133571659327481</v>
+        <v>5.122414880822375</v>
       </c>
       <c r="N21" t="n">
-        <v>36.91620480360921</v>
+        <v>36.80866295872059</v>
       </c>
       <c r="O21" t="n">
-        <v>6.075870703332092</v>
+        <v>6.067014336452535</v>
       </c>
       <c r="P21" t="n">
-        <v>355.2747342924698</v>
+        <v>355.2591053399686</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34113,28 +34219,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5463922868851337</v>
+        <v>0.5468393386758985</v>
       </c>
       <c r="J22" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K22" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2127374716845649</v>
+        <v>0.2143499042583781</v>
       </c>
       <c r="M22" t="n">
-        <v>6.544884804977065</v>
+        <v>6.524887897908215</v>
       </c>
       <c r="N22" t="n">
-        <v>58.70481939310894</v>
+        <v>58.51111706210501</v>
       </c>
       <c r="O22" t="n">
-        <v>7.661907033703094</v>
+        <v>7.64925598095037</v>
       </c>
       <c r="P22" t="n">
-        <v>352.5527569271743</v>
+        <v>352.5481185443273</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34191,28 +34297,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9803010923664613</v>
+        <v>0.9799503369481208</v>
       </c>
       <c r="J23" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K23" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5363490842782611</v>
+        <v>0.5381524664454275</v>
       </c>
       <c r="M23" t="n">
-        <v>5.394622477727151</v>
+        <v>5.378479833484533</v>
       </c>
       <c r="N23" t="n">
-        <v>44.14195875455214</v>
+        <v>43.99612664588338</v>
       </c>
       <c r="O23" t="n">
-        <v>6.643941507460172</v>
+        <v>6.632957609233108</v>
       </c>
       <c r="P23" t="n">
-        <v>342.9343280549459</v>
+        <v>342.9379673154288</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34269,28 +34375,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6788899657821136</v>
+        <v>0.6787704715417798</v>
       </c>
       <c r="J24" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K24" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4151930212596585</v>
+        <v>0.4170476433164049</v>
       </c>
       <c r="M24" t="n">
-        <v>4.882178425685111</v>
+        <v>4.866548754142463</v>
       </c>
       <c r="N24" t="n">
-        <v>34.49453779062218</v>
+        <v>34.38003304138517</v>
       </c>
       <c r="O24" t="n">
-        <v>5.873205069689137</v>
+        <v>5.86344890328083</v>
       </c>
       <c r="P24" t="n">
-        <v>354.2422370170981</v>
+        <v>354.2434768287847</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34347,28 +34453,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7094747381026312</v>
+        <v>0.7062270206894976</v>
       </c>
       <c r="J25" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K25" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L25" t="n">
-        <v>0.447854208755191</v>
+        <v>0.4470328554756827</v>
       </c>
       <c r="M25" t="n">
-        <v>4.784478785459598</v>
+        <v>4.78146258527696</v>
       </c>
       <c r="N25" t="n">
-        <v>32.9746373559047</v>
+        <v>32.93529523147839</v>
       </c>
       <c r="O25" t="n">
-        <v>5.742354687399995</v>
+        <v>5.738928055959439</v>
       </c>
       <c r="P25" t="n">
-        <v>361.6046945436892</v>
+        <v>361.6383912138563</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34425,28 +34531,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5981350972658771</v>
+        <v>0.5945826339317981</v>
       </c>
       <c r="J26" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K26" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3912891018839498</v>
+        <v>0.3896774189553537</v>
       </c>
       <c r="M26" t="n">
-        <v>4.345630737559962</v>
+        <v>4.349088163015371</v>
       </c>
       <c r="N26" t="n">
-        <v>29.5733788873441</v>
+        <v>29.55913060255779</v>
       </c>
       <c r="O26" t="n">
-        <v>5.438141124257819</v>
+        <v>5.436830933784661</v>
       </c>
       <c r="P26" t="n">
-        <v>347.2004062344785</v>
+        <v>347.2372647938979</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34503,28 +34609,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4048580366054518</v>
+        <v>0.4029090275980843</v>
       </c>
       <c r="J27" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K27" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2530517544076287</v>
+        <v>0.2525512781886758</v>
       </c>
       <c r="M27" t="n">
-        <v>3.94439240118686</v>
+        <v>3.942048750522314</v>
       </c>
       <c r="N27" t="n">
-        <v>25.70844077053164</v>
+        <v>25.64831542924362</v>
       </c>
       <c r="O27" t="n">
-        <v>5.070349176391271</v>
+        <v>5.064416593176713</v>
       </c>
       <c r="P27" t="n">
-        <v>345.1157017019227</v>
+        <v>345.1359236317643</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34581,28 +34687,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2394539659859856</v>
+        <v>0.2379250603381278</v>
       </c>
       <c r="J28" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K28" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L28" t="n">
-        <v>0.099727933545249</v>
+        <v>0.09924503451654787</v>
       </c>
       <c r="M28" t="n">
-        <v>4.083610658413964</v>
+        <v>4.077482718209564</v>
       </c>
       <c r="N28" t="n">
-        <v>27.50363355370894</v>
+        <v>27.42781874452035</v>
       </c>
       <c r="O28" t="n">
-        <v>5.244390675160361</v>
+        <v>5.237157506178361</v>
       </c>
       <c r="P28" t="n">
-        <v>360.7915099073145</v>
+        <v>360.8073730575763</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34659,28 +34765,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1146010104730588</v>
+        <v>0.1128366115710795</v>
       </c>
       <c r="J29" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K29" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L29" t="n">
-        <v>0.03483279793088967</v>
+        <v>0.03403099747480809</v>
       </c>
       <c r="M29" t="n">
-        <v>3.316387307130829</v>
+        <v>3.315140187169319</v>
       </c>
       <c r="N29" t="n">
-        <v>19.33660109691312</v>
+        <v>19.29308156553612</v>
       </c>
       <c r="O29" t="n">
-        <v>4.397340229833612</v>
+        <v>4.39238904988346</v>
       </c>
       <c r="P29" t="n">
-        <v>372.2169627298147</v>
+        <v>372.23526923875</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34718,7 +34824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD301"/>
+  <dimension ref="A1:AD302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80081,6 +80187,158 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>-36.66823781029512,175.55796179688295</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>-36.66884404675598,175.55740795860413</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-36.6695081979193,175.55705596960505</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-36.670157137008324,175.5566509879516</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-36.67082505488907,175.55631216648564</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-36.671483852526244,175.5560215533468</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-36.672164126522546,175.5558274906733</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-36.672871026928945,175.55563642888816</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-36.67357657962125,175.555402193369</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-36.67429032593839,175.55527337972472</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-36.675005598298185,175.55516427020484</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-36.675719484647466,175.55501729194256</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-36.67643966585103,175.55495320758234</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-36.67715849944617,175.5548927122954</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-36.67788093616834,175.55487434945087</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-36.67859976665243,175.55491079003156</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>-36.67931727550707,175.5550001360337</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>-36.68002964311566,175.55513496125377</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>-36.68073471833583,175.55532209031009</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>-36.681430532689305,175.5555007526258</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>-36.682136448066146,175.55565935919205</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>-36.682830801823954,175.5558983673294</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>-36.6835177919475,175.5561694325023</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>-36.684181546153624,175.55642869399085</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>-36.68483680877465,175.55677625860548</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>-36.685434691598225,175.557282942664</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>-36.68593336554679,175.55793054708536</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>-36.68628035407251,175.5586992147823</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD302"/>
+  <dimension ref="A1:AD305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29002,7 +29002,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>417.17</v>
+        <v>407.56</v>
       </c>
       <c r="C300" t="n">
         <v>407.05</v>
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>417.17</v>
+        <v>407.56</v>
       </c>
       <c r="C301" t="n">
         <v>407.05</v>
@@ -29194,7 +29194,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>417.17</v>
+        <v>407.56</v>
       </c>
       <c r="C302" t="n">
         <v>394.64</v>
@@ -29280,6 +29280,294 @@
       <c r="AD302" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>402.6</v>
+      </c>
+      <c r="C303" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="D303" t="n">
+        <v>389.16</v>
+      </c>
+      <c r="E303" t="n">
+        <v>381.17</v>
+      </c>
+      <c r="F303" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="G303" t="n">
+        <v>381.12</v>
+      </c>
+      <c r="H303" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="I303" t="n">
+        <v>365.86</v>
+      </c>
+      <c r="J303" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="K303" t="n">
+        <v>351.76</v>
+      </c>
+      <c r="L303" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="M303" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="N303" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="O303" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="P303" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="R303" t="n">
+        <v>356.76</v>
+      </c>
+      <c r="S303" t="n">
+        <v>359.03</v>
+      </c>
+      <c r="T303" t="n">
+        <v>366.96</v>
+      </c>
+      <c r="U303" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="V303" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="W303" t="n">
+        <v>364.52</v>
+      </c>
+      <c r="X303" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>364.94</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>403.55</v>
+      </c>
+      <c r="C304" t="n">
+        <v>391.72</v>
+      </c>
+      <c r="D304" t="n">
+        <v>387.74</v>
+      </c>
+      <c r="E304" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="F304" t="n">
+        <v>380.32</v>
+      </c>
+      <c r="G304" t="n">
+        <v>381.14</v>
+      </c>
+      <c r="H304" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="I304" t="n">
+        <v>365.17</v>
+      </c>
+      <c r="J304" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="K304" t="n">
+        <v>351.73</v>
+      </c>
+      <c r="L304" t="n">
+        <v>350.84</v>
+      </c>
+      <c r="M304" t="n">
+        <v>347.03</v>
+      </c>
+      <c r="N304" t="n">
+        <v>348.44</v>
+      </c>
+      <c r="O304" t="n">
+        <v>350.02</v>
+      </c>
+      <c r="P304" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="R304" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="S304" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="T304" t="n">
+        <v>367.37</v>
+      </c>
+      <c r="U304" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="V304" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="W304" t="n">
+        <v>365.37</v>
+      </c>
+      <c r="X304" t="n">
+        <v>370.02</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>359.45</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>354</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>364.94</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>406.76</v>
+      </c>
+      <c r="C305" t="n">
+        <v>391.72</v>
+      </c>
+      <c r="D305" t="n">
+        <v>390.58</v>
+      </c>
+      <c r="E305" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="F305" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="G305" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="H305" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="I305" t="n">
+        <v>364.11</v>
+      </c>
+      <c r="J305" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="K305" t="n">
+        <v>351.51</v>
+      </c>
+      <c r="L305" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="M305" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="N305" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="O305" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="P305" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="R305" t="n">
+        <v>357.19</v>
+      </c>
+      <c r="S305" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="T305" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="U305" t="n">
+        <v>368.04</v>
+      </c>
+      <c r="V305" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="W305" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="X305" t="n">
+        <v>366.93</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>373.77</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32487,6 +32775,36 @@
       </c>
       <c r="B319" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -32655,28 +32973,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.958822798589178</v>
+        <v>-6.915342641347194</v>
       </c>
       <c r="J2" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K2" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7703080828051827</v>
+        <v>0.7722037213695507</v>
       </c>
       <c r="M2" t="n">
-        <v>19.63552216488234</v>
+        <v>19.61103735207511</v>
       </c>
       <c r="N2" t="n">
-        <v>704.1145265240098</v>
+        <v>697.7906032774902</v>
       </c>
       <c r="O2" t="n">
-        <v>26.53515642546714</v>
+        <v>26.41572643857235</v>
       </c>
       <c r="P2" t="n">
-        <v>560.9176390524211</v>
+        <v>560.4245113233634</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32737,28 +33055,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.714647923277984</v>
+        <v>-3.707817511076704</v>
       </c>
       <c r="J3" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K3" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4829556110127347</v>
+        <v>0.488242009455424</v>
       </c>
       <c r="M3" t="n">
-        <v>22.46612977969165</v>
+        <v>22.25793316665619</v>
       </c>
       <c r="N3" t="n">
-        <v>787.0528294784174</v>
+        <v>778.8409717772062</v>
       </c>
       <c r="O3" t="n">
-        <v>28.05446184617373</v>
+        <v>27.90772243980519</v>
       </c>
       <c r="P3" t="n">
-        <v>486.9876904420155</v>
+        <v>486.9156211495542</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32815,28 +33133,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.222461623938193</v>
+        <v>2.158879145426946</v>
       </c>
       <c r="J4" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K4" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1747355683356572</v>
+        <v>0.1689898886954692</v>
       </c>
       <c r="M4" t="n">
-        <v>29.43433493563135</v>
+        <v>29.45905585564773</v>
       </c>
       <c r="N4" t="n">
-        <v>1253.891389760144</v>
+        <v>1249.017667302778</v>
       </c>
       <c r="O4" t="n">
-        <v>35.41032885698951</v>
+        <v>35.34144404665403</v>
       </c>
       <c r="P4" t="n">
-        <v>359.0276915866715</v>
+        <v>359.7023828312338</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32893,28 +33211,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.774464384352385</v>
+        <v>1.733841392427127</v>
       </c>
       <c r="J5" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K5" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5608347290294602</v>
+        <v>0.5486568461021604</v>
       </c>
       <c r="M5" t="n">
-        <v>8.990377053222367</v>
+        <v>9.067802463594651</v>
       </c>
       <c r="N5" t="n">
-        <v>128.2409272020867</v>
+        <v>130.4796367867997</v>
       </c>
       <c r="O5" t="n">
-        <v>11.32435107200791</v>
+        <v>11.42276835039561</v>
       </c>
       <c r="P5" t="n">
-        <v>352.6734395299455</v>
+        <v>353.1060139024562</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32971,28 +33289,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7075694808800551</v>
+        <v>0.7029624980114673</v>
       </c>
       <c r="J6" t="n">
+        <v>304</v>
+      </c>
+      <c r="K6" t="n">
         <v>301</v>
       </c>
-      <c r="K6" t="n">
-        <v>298</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.4055145572751689</v>
+        <v>0.4079008527144009</v>
       </c>
       <c r="M6" t="n">
-        <v>3.197647722047766</v>
+        <v>3.184374216348198</v>
       </c>
       <c r="N6" t="n">
-        <v>37.92871006648505</v>
+        <v>37.60339364222525</v>
       </c>
       <c r="O6" t="n">
-        <v>6.158628911250056</v>
+        <v>6.132160601470353</v>
       </c>
       <c r="P6" t="n">
-        <v>363.859496829086</v>
+        <v>363.9086967869019</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33049,28 +33367,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2455266129812995</v>
+        <v>0.2417975712776457</v>
       </c>
       <c r="J7" t="n">
+        <v>304</v>
+      </c>
+      <c r="K7" t="n">
         <v>301</v>
       </c>
-      <c r="K7" t="n">
-        <v>298</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02942946743658503</v>
+        <v>0.02923438317368976</v>
       </c>
       <c r="M7" t="n">
-        <v>4.237685491972638</v>
+        <v>4.219863745086339</v>
       </c>
       <c r="N7" t="n">
-        <v>104.5247407697453</v>
+        <v>103.5171266415129</v>
       </c>
       <c r="O7" t="n">
-        <v>10.22373418911824</v>
+        <v>10.17433666837858</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8193626769083</v>
+        <v>376.8588212670476</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33127,28 +33445,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04316132207461834</v>
+        <v>0.04468271199991279</v>
       </c>
       <c r="J8" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K8" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001148181028473472</v>
+        <v>0.001260225858866315</v>
       </c>
       <c r="M8" t="n">
-        <v>6.065689288413964</v>
+        <v>6.01125800299714</v>
       </c>
       <c r="N8" t="n">
-        <v>85.67153598559906</v>
+        <v>84.82921804854664</v>
       </c>
       <c r="O8" t="n">
-        <v>9.255891960562151</v>
+        <v>9.210277848607317</v>
       </c>
       <c r="P8" t="n">
-        <v>372.923043489156</v>
+        <v>372.9070116576199</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33205,28 +33523,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01411121956200222</v>
+        <v>-0.02418880114085572</v>
       </c>
       <c r="J9" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K9" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L9" t="n">
-        <v>8.049833821188734e-05</v>
+        <v>0.0002418323109567577</v>
       </c>
       <c r="M9" t="n">
-        <v>7.874145899495981</v>
+        <v>7.844481361153367</v>
       </c>
       <c r="N9" t="n">
-        <v>131.5978091915793</v>
+        <v>130.5115305093009</v>
       </c>
       <c r="O9" t="n">
-        <v>11.47160883187617</v>
+        <v>11.42416432433029</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2431048749712</v>
+        <v>370.3489329859125</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33283,28 +33601,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3519295948721602</v>
+        <v>-0.3590827392419589</v>
       </c>
       <c r="J10" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K10" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0464392247700236</v>
+        <v>0.04933896010849514</v>
       </c>
       <c r="M10" t="n">
-        <v>8.258002054460391</v>
+        <v>8.208074109161906</v>
       </c>
       <c r="N10" t="n">
-        <v>132.8556908451187</v>
+        <v>131.6485364016042</v>
       </c>
       <c r="O10" t="n">
-        <v>11.52630430125453</v>
+        <v>11.4738196082039</v>
       </c>
       <c r="P10" t="n">
-        <v>365.9534325307212</v>
+        <v>366.029283052308</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33361,28 +33679,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01732112991512446</v>
+        <v>-0.02364259181563802</v>
       </c>
       <c r="J11" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K11" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001797740458919783</v>
+        <v>0.0003427824297445037</v>
       </c>
       <c r="M11" t="n">
-        <v>6.186401473864565</v>
+        <v>6.145876708973196</v>
       </c>
       <c r="N11" t="n">
-        <v>86.25361609090753</v>
+        <v>85.47633697034323</v>
       </c>
       <c r="O11" t="n">
-        <v>9.287282492252915</v>
+        <v>9.245341365809228</v>
       </c>
       <c r="P11" t="n">
-        <v>355.0959739954792</v>
+        <v>355.1636088615049</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33439,28 +33757,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1270270019649651</v>
+        <v>0.1182999761177228</v>
       </c>
       <c r="J12" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K12" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02600503142463761</v>
+        <v>0.02304723149698928</v>
       </c>
       <c r="M12" t="n">
-        <v>4.330133901997576</v>
+        <v>4.326825669951313</v>
       </c>
       <c r="N12" t="n">
-        <v>32.26297737998765</v>
+        <v>32.11742455321296</v>
       </c>
       <c r="O12" t="n">
-        <v>5.680050825475741</v>
+        <v>5.667223707708472</v>
       </c>
       <c r="P12" t="n">
-        <v>351.3154969371713</v>
+        <v>351.4066371793978</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33517,28 +33835,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2156149183378585</v>
+        <v>0.2016688371616157</v>
       </c>
       <c r="J13" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K13" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1096434402814651</v>
+        <v>0.09746112748853608</v>
       </c>
       <c r="M13" t="n">
-        <v>3.426735255167354</v>
+        <v>3.450287950278434</v>
       </c>
       <c r="N13" t="n">
-        <v>20.1535676778362</v>
+        <v>20.39053721446971</v>
       </c>
       <c r="O13" t="n">
-        <v>4.489272510979502</v>
+        <v>4.515588246781332</v>
       </c>
       <c r="P13" t="n">
-        <v>348.3517931688241</v>
+        <v>348.4974499947919</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33595,28 +33913,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.15155859069213</v>
+        <v>0.1430833634463984</v>
       </c>
       <c r="J14" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K14" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05534592321426657</v>
+        <v>0.05039336663271865</v>
       </c>
       <c r="M14" t="n">
-        <v>3.627704495369361</v>
+        <v>3.634522339948941</v>
       </c>
       <c r="N14" t="n">
-        <v>20.92961791987457</v>
+        <v>20.88647941397336</v>
       </c>
       <c r="O14" t="n">
-        <v>4.574889935274352</v>
+        <v>4.570172799137179</v>
       </c>
       <c r="P14" t="n">
-        <v>349.0769659074541</v>
+        <v>349.1654807511667</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33673,28 +33991,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.284391383819714</v>
+        <v>0.2714899889203443</v>
       </c>
       <c r="J15" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K15" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1870483855586981</v>
+        <v>0.1738973501316995</v>
       </c>
       <c r="M15" t="n">
-        <v>3.409069547594184</v>
+        <v>3.435850620711106</v>
       </c>
       <c r="N15" t="n">
-        <v>18.76534785991585</v>
+        <v>18.95681123013166</v>
       </c>
       <c r="O15" t="n">
-        <v>4.331898874617902</v>
+        <v>4.353942033391311</v>
       </c>
       <c r="P15" t="n">
-        <v>349.3531872125556</v>
+        <v>349.4879290406444</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33751,28 +34069,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3485543406968052</v>
+        <v>0.3372865621157163</v>
       </c>
       <c r="J16" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K16" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2455913215169516</v>
+        <v>0.2353360363153097</v>
       </c>
       <c r="M16" t="n">
-        <v>3.259515331873983</v>
+        <v>3.28605948242591</v>
       </c>
       <c r="N16" t="n">
-        <v>19.92267579214727</v>
+        <v>20.01229340263636</v>
       </c>
       <c r="O16" t="n">
-        <v>4.463482473601444</v>
+        <v>4.473510188055501</v>
       </c>
       <c r="P16" t="n">
-        <v>351.4914440050284</v>
+        <v>351.609127216094</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33829,28 +34147,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4592623153922726</v>
+        <v>0.4493023594229656</v>
       </c>
       <c r="J17" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K17" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3633204470205976</v>
+        <v>0.3561352692905304</v>
       </c>
       <c r="M17" t="n">
-        <v>3.351513522714553</v>
+        <v>3.364522856512767</v>
       </c>
       <c r="N17" t="n">
-        <v>19.7317544184451</v>
+        <v>19.75939504125492</v>
       </c>
       <c r="O17" t="n">
-        <v>4.442043946028123</v>
+        <v>4.445154107705932</v>
       </c>
       <c r="P17" t="n">
-        <v>350.9406693742422</v>
+        <v>351.0446946119967</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33907,28 +34225,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5552847120253033</v>
+        <v>0.5469515810873872</v>
       </c>
       <c r="J18" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K18" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4414815979130997</v>
+        <v>0.4380850051815894</v>
       </c>
       <c r="M18" t="n">
-        <v>3.604902162038522</v>
+        <v>3.612841734638005</v>
       </c>
       <c r="N18" t="n">
-        <v>20.8242481956268</v>
+        <v>20.77430924300512</v>
       </c>
       <c r="O18" t="n">
-        <v>4.563359310379449</v>
+        <v>4.557884294604802</v>
       </c>
       <c r="P18" t="n">
-        <v>346.3815750175248</v>
+        <v>346.4686084493709</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33985,28 +34303,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5809161107457349</v>
+        <v>0.5732551796425855</v>
       </c>
       <c r="J19" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K19" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4123817903931483</v>
+        <v>0.4104654020336098</v>
       </c>
       <c r="M19" t="n">
-        <v>4.057260221688009</v>
+        <v>4.058770630397942</v>
       </c>
       <c r="N19" t="n">
-        <v>25.67057666069502</v>
+        <v>25.55320098820901</v>
       </c>
       <c r="O19" t="n">
-        <v>5.066613924574776</v>
+        <v>5.055017407310188</v>
       </c>
       <c r="P19" t="n">
-        <v>347.2437934188735</v>
+        <v>347.3238173067427</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34063,28 +34381,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5932629301157878</v>
+        <v>0.5893502144809716</v>
       </c>
       <c r="J20" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K20" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3798313981010938</v>
+        <v>0.381923066236081</v>
       </c>
       <c r="M20" t="n">
-        <v>4.488259590520625</v>
+        <v>4.465881673716871</v>
       </c>
       <c r="N20" t="n">
-        <v>30.67795134717415</v>
+        <v>30.43197472885673</v>
       </c>
       <c r="O20" t="n">
-        <v>5.538768035147722</v>
+        <v>5.51651835208193</v>
       </c>
       <c r="P20" t="n">
-        <v>352.2426979708846</v>
+        <v>352.2835902364554</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34141,28 +34459,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6359579753804582</v>
+        <v>0.6307782160177589</v>
       </c>
       <c r="J21" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K21" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3697094793684285</v>
+        <v>0.3710097012197158</v>
       </c>
       <c r="M21" t="n">
-        <v>5.122414880822375</v>
+        <v>5.09994270901581</v>
       </c>
       <c r="N21" t="n">
-        <v>36.80866295872059</v>
+        <v>36.51982176385415</v>
       </c>
       <c r="O21" t="n">
-        <v>6.067014336452535</v>
+        <v>6.043163224988562</v>
       </c>
       <c r="P21" t="n">
-        <v>355.2591053399686</v>
+        <v>355.3132216021849</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34219,28 +34537,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5468393386758985</v>
+        <v>0.5455427804946609</v>
       </c>
       <c r="J22" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K22" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2143499042583781</v>
+        <v>0.2174221720173944</v>
       </c>
       <c r="M22" t="n">
-        <v>6.524887897908215</v>
+        <v>6.481888832364252</v>
       </c>
       <c r="N22" t="n">
-        <v>58.51111706210501</v>
+        <v>57.99598513754246</v>
       </c>
       <c r="O22" t="n">
-        <v>7.64925598095037</v>
+        <v>7.615509512668372</v>
       </c>
       <c r="P22" t="n">
-        <v>352.5481185443273</v>
+        <v>352.5616974064282</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34297,28 +34615,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9799503369481208</v>
+        <v>0.9691361900327984</v>
       </c>
       <c r="J23" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K23" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5381524664454275</v>
+        <v>0.5369384719736807</v>
       </c>
       <c r="M23" t="n">
-        <v>5.378479833484533</v>
+        <v>5.379130353779282</v>
       </c>
       <c r="N23" t="n">
-        <v>43.99612664588338</v>
+        <v>43.85310975591614</v>
       </c>
       <c r="O23" t="n">
-        <v>6.632957609233108</v>
+        <v>6.622168055547681</v>
       </c>
       <c r="P23" t="n">
-        <v>342.9379673154288</v>
+        <v>343.050944914693</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34375,28 +34693,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6787704715417798</v>
+        <v>0.6716758866217404</v>
       </c>
       <c r="J24" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K24" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4170476433164049</v>
+        <v>0.4168331860356047</v>
       </c>
       <c r="M24" t="n">
-        <v>4.866548754142463</v>
+        <v>4.85272491005805</v>
       </c>
       <c r="N24" t="n">
-        <v>34.38003304138517</v>
+        <v>34.1717030171167</v>
       </c>
       <c r="O24" t="n">
-        <v>5.86344890328083</v>
+        <v>5.845656765250308</v>
       </c>
       <c r="P24" t="n">
-        <v>354.2434768287847</v>
+        <v>354.3176004722528</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34453,28 +34771,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7062270206894976</v>
+        <v>0.694290688464316</v>
       </c>
       <c r="J25" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K25" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4470328554756827</v>
+        <v>0.4420883922128643</v>
       </c>
       <c r="M25" t="n">
-        <v>4.78146258527696</v>
+        <v>4.782028501464905</v>
       </c>
       <c r="N25" t="n">
-        <v>32.93529523147839</v>
+        <v>32.93484028575133</v>
       </c>
       <c r="O25" t="n">
-        <v>5.738928055959439</v>
+        <v>5.738888419001657</v>
       </c>
       <c r="P25" t="n">
-        <v>361.6383912138563</v>
+        <v>361.7630667611963</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34531,28 +34849,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5945826339317981</v>
+        <v>0.5848198039138436</v>
       </c>
       <c r="J26" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K26" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3896774189553537</v>
+        <v>0.3857350328289232</v>
       </c>
       <c r="M26" t="n">
-        <v>4.349088163015371</v>
+        <v>4.35477112304746</v>
       </c>
       <c r="N26" t="n">
-        <v>29.55913060255779</v>
+        <v>29.48678343279538</v>
       </c>
       <c r="O26" t="n">
-        <v>5.436830933784661</v>
+        <v>5.430173425664726</v>
       </c>
       <c r="P26" t="n">
-        <v>347.2372647938979</v>
+        <v>347.3392361514299</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34609,28 +34927,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4029090275980843</v>
+        <v>0.3973836352996605</v>
       </c>
       <c r="J27" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K27" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2525512781886758</v>
+        <v>0.2513301816062077</v>
       </c>
       <c r="M27" t="n">
-        <v>3.942048750522314</v>
+        <v>3.933173693931341</v>
       </c>
       <c r="N27" t="n">
-        <v>25.64831542924362</v>
+        <v>25.46726058578954</v>
       </c>
       <c r="O27" t="n">
-        <v>5.064416593176713</v>
+        <v>5.046509742959934</v>
       </c>
       <c r="P27" t="n">
-        <v>345.1359236317643</v>
+        <v>345.1936382179094</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34687,28 +35005,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2379250603381278</v>
+        <v>0.232605184324963</v>
       </c>
       <c r="J28" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K28" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L28" t="n">
-        <v>0.09924503451654787</v>
+        <v>0.09714786642514284</v>
       </c>
       <c r="M28" t="n">
-        <v>4.077482718209564</v>
+        <v>4.062521567814516</v>
       </c>
       <c r="N28" t="n">
-        <v>27.42781874452035</v>
+        <v>27.22317260213058</v>
       </c>
       <c r="O28" t="n">
-        <v>5.237157506178361</v>
+        <v>5.217583023022305</v>
       </c>
       <c r="P28" t="n">
-        <v>360.8073730575763</v>
+        <v>360.8629479903412</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34765,28 +35083,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1128366115710795</v>
+        <v>0.1067414638078689</v>
       </c>
       <c r="J29" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K29" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L29" t="n">
-        <v>0.03403099747480809</v>
+        <v>0.0311378545051848</v>
       </c>
       <c r="M29" t="n">
-        <v>3.315140187169319</v>
+        <v>3.315805173341084</v>
       </c>
       <c r="N29" t="n">
-        <v>19.29308156553612</v>
+        <v>19.19358967764864</v>
       </c>
       <c r="O29" t="n">
-        <v>4.39238904988346</v>
+        <v>4.381048924361452</v>
       </c>
       <c r="P29" t="n">
-        <v>372.23526923875</v>
+        <v>372.2989456274483</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34824,7 +35142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD302"/>
+  <dimension ref="A1:AD305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79891,7 +80209,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>-36.66823781029512,175.55796179688295</t>
+          <t>-36.6682087592852,175.55786055587058</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -80043,7 +80361,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>-36.66823781029512,175.55796179688295</t>
+          <t>-36.6682087592852,175.55786055587058</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -80195,7 +80513,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>-36.66823781029512,175.55796179688295</t>
+          <t>-36.6682087592852,175.55786055587058</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -80336,6 +80654,462 @@
       <c r="AD302" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>-36.668193765180625,175.55780830247292</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>-36.66883277084441,175.55736866291804</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>-36.6695018192821,175.55703374049904</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-36.67015199778173,175.55663307810855</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-36.67082127602401,175.5562989973767</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-36.67148072531446,175.55600523296783</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-36.67216226084737,175.55580659284527</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-36.67286897469658,175.555610045463</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-36.673573488226026,175.55536245088658</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-36.67428843818497,175.5552491109812</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-36.6750024895505,175.5551243043347</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-36.67571784913716,175.5549922089893</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-36.67643884015176,175.55493724656165</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-36.677157943621395,175.554881773078</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>-36.67788072654788,175.55486283209018</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-36.67860060603068,175.55489639924133</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>-36.679319489238395,175.55497849920667</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>-36.680033060244064,175.55510156256872</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>-36.68073893930641,175.55528702273074</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>-36.681438939656154,175.55545494869492</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>-36.682136448066146,175.55565935919205</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>-36.68284015886622,175.55585759729382</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>-36.683523741988814,175.556143507284</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>-36.68418686367387,175.55641536229768</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>-36.68483680877465,175.55677625860548</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>-36.685434691598225,175.557282942664</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>-36.68593336554679,175.55793054708536</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>-36.68628035407251,175.5586992147823</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>-36.668196637037184,175.55781831068268</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>-36.66883521950195,175.5573771962967</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>-36.669497526547524,175.5570187806287</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-36.67015003278258,175.556626230228</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-36.67082375495966,175.55630763631206</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-36.67148076701064,175.55600545057288</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-36.6721635410185,175.5558209323123</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-36.672868377210094,175.5556023642128</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-36.67357439746131,175.55537413985175</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-36.674288412206685,175.55524877700768</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-36.675003468071424,175.55513688412086</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-36.67571784186821,175.55499209750948</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-36.67643863228308,175.55493322840258</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-36.677157784814135,175.55487864758732</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>-36.67788064921189,175.55485858296683</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>-36.67860067760549,175.55489517211967</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>-36.67931881944318,175.55498504573399</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>-36.68003218609582,175.5551101064187</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>-36.680738393377034,175.55529155828543</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>-36.68143697803211,175.55546563627976</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>-36.68213383107229,175.55567076179665</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>-36.6828380603223,175.55586674097026</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>-36.683522655674636,175.55614824051918</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>-36.68418146619089,175.55642889446742</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>-36.6848284245955,175.55678970164</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>-36.68542923383238,175.55729141662957</t>
+        </is>
+      </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>-36.68593336554679,175.55793054708536</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>-36.68627759388509,175.5587015352344</t>
+        </is>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>-36.66820634088284,175.55785212790192</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>-36.66883521950195,175.5573771962967</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-36.669506112014716,175.55704870037096</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-36.67015003278258,175.556626230228</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-36.67082777567098,175.55632164824482</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-36.67148345641288,175.55601948609873</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-36.672162280694984,175.55580681516258</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-36.67286745933134,175.55559056403158</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-36.67357369605133,175.55536512265002</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-36.67428822169917,175.5552463278685</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-36.6750034767309,175.55513699544642</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-36.675718496072996,175.5550021306907</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-36.676439394467586,175.55494796165246</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-36.67715872064145,175.5548970656575</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-36.67788091174659,175.5548730076224</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-36.67860020260879,175.5549033157452</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>-36.679319001082604,175.55498327040456</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>-36.68003415009037,175.5550909104957</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>-36.680742893960435,175.55525416761296</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>-36.681442782835255,175.55543400975142</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>-36.68214765668819,175.5556105216121</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>-36.68284803457198,175.55582328160918</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>-36.68353028455901,175.5561150002962</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>-36.68418930253607,175.55640924776108</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>-36.6848389048192,175.5567728978464</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>-36.68543784247311,175.5572780504771</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>-36.68594096964613,175.5579218099916</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>-36.686293036014234,175.55868855324366</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD305"/>
+  <dimension ref="A1:AD307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29566,6 +29566,198 @@
         <v>371.03</v>
       </c>
       <c r="AD305" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>406.76</v>
+      </c>
+      <c r="C306" t="n">
+        <v>391.72</v>
+      </c>
+      <c r="D306" t="n">
+        <v>390.58</v>
+      </c>
+      <c r="E306" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="F306" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="G306" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="H306" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="I306" t="n">
+        <v>364.11</v>
+      </c>
+      <c r="J306" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="K306" t="n">
+        <v>351.51</v>
+      </c>
+      <c r="L306" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="M306" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="N306" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="O306" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="P306" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="R306" t="n">
+        <v>357.19</v>
+      </c>
+      <c r="S306" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="T306" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="U306" t="n">
+        <v>368.04</v>
+      </c>
+      <c r="V306" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="W306" t="n">
+        <v>358.83</v>
+      </c>
+      <c r="X306" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>354.58</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>408.96</v>
+      </c>
+      <c r="C307" t="n">
+        <v>418.88</v>
+      </c>
+      <c r="D307" t="n">
+        <v>390.58</v>
+      </c>
+      <c r="E307" t="n">
+        <v>378.74</v>
+      </c>
+      <c r="F307" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="G307" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="H307" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="I307" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="J307" t="n">
+        <v>352.43</v>
+      </c>
+      <c r="K307" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="L307" t="n">
+        <v>350.82</v>
+      </c>
+      <c r="M307" t="n">
+        <v>348.88</v>
+      </c>
+      <c r="N307" t="n">
+        <v>351.07</v>
+      </c>
+      <c r="O307" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="P307" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="R307" t="n">
+        <v>358.18</v>
+      </c>
+      <c r="S307" t="n">
+        <v>359.02</v>
+      </c>
+      <c r="T307" t="n">
+        <v>364.35</v>
+      </c>
+      <c r="U307" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="V307" t="n">
+        <v>356.33</v>
+      </c>
+      <c r="W307" t="n">
+        <v>359.16</v>
+      </c>
+      <c r="X307" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>354.28</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="AD307" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29582,7 +29774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32804,6 +32996,26 @@
         </is>
       </c>
       <c r="B322" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
         <v>-0.6</v>
       </c>
     </row>
@@ -32973,28 +33185,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.915342641347194</v>
+        <v>-6.867543698372222</v>
       </c>
       <c r="J2" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K2" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7722037213695507</v>
+        <v>0.770870355299889</v>
       </c>
       <c r="M2" t="n">
-        <v>19.61103735207511</v>
+        <v>19.67945860965538</v>
       </c>
       <c r="N2" t="n">
-        <v>697.7906032774902</v>
+        <v>699.7587500518913</v>
       </c>
       <c r="O2" t="n">
-        <v>26.41572643857235</v>
+        <v>26.45295352227972</v>
       </c>
       <c r="P2" t="n">
-        <v>560.4245113233634</v>
+        <v>559.8834283505437</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33055,28 +33267,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.707817511076704</v>
+        <v>-3.68333812404501</v>
       </c>
       <c r="J3" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K3" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L3" t="n">
-        <v>0.488242009455424</v>
+        <v>0.4879184084332906</v>
       </c>
       <c r="M3" t="n">
-        <v>22.25793316665619</v>
+        <v>22.2074213911498</v>
       </c>
       <c r="N3" t="n">
-        <v>778.8409717772062</v>
+        <v>776.6896785077483</v>
       </c>
       <c r="O3" t="n">
-        <v>27.90772243980519</v>
+        <v>27.86915281288163</v>
       </c>
       <c r="P3" t="n">
-        <v>486.9156211495542</v>
+        <v>486.6566289583723</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33133,28 +33345,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.158879145426946</v>
+        <v>2.120542725741029</v>
       </c>
       <c r="J4" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K4" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1689898886954692</v>
+        <v>0.1656746750892782</v>
       </c>
       <c r="M4" t="n">
-        <v>29.45905585564773</v>
+        <v>29.45229130972831</v>
       </c>
       <c r="N4" t="n">
-        <v>1249.017667302778</v>
+        <v>1244.991180404753</v>
       </c>
       <c r="O4" t="n">
-        <v>35.34144404665403</v>
+        <v>35.28443255041454</v>
       </c>
       <c r="P4" t="n">
-        <v>359.7023828312338</v>
+        <v>360.1102537075555</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33211,28 +33423,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.733841392427127</v>
+        <v>1.706424127404367</v>
       </c>
       <c r="J5" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K5" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5486568461021604</v>
+        <v>0.5399250255871284</v>
       </c>
       <c r="M5" t="n">
-        <v>9.067802463594651</v>
+        <v>9.126302313235874</v>
       </c>
       <c r="N5" t="n">
-        <v>130.4796367867997</v>
+        <v>132.1226493932971</v>
       </c>
       <c r="O5" t="n">
-        <v>11.42276835039561</v>
+        <v>11.49446168349337</v>
       </c>
       <c r="P5" t="n">
-        <v>353.1060139024562</v>
+        <v>353.3986786907386</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33289,28 +33501,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7029624980114673</v>
+        <v>0.7017088091652999</v>
       </c>
       <c r="J6" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4079008527144009</v>
+        <v>0.4108302980850603</v>
       </c>
       <c r="M6" t="n">
-        <v>3.184374216348198</v>
+        <v>3.168411423904888</v>
       </c>
       <c r="N6" t="n">
-        <v>37.60339364222525</v>
+        <v>37.36043322464337</v>
       </c>
       <c r="O6" t="n">
-        <v>6.132160601470353</v>
+        <v>6.112318154730116</v>
       </c>
       <c r="P6" t="n">
-        <v>363.9086967869019</v>
+        <v>363.922122807386</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33367,28 +33579,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2417975712776457</v>
+        <v>0.2406267128112183</v>
       </c>
       <c r="J7" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K7" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02923438317368976</v>
+        <v>0.02940230316869863</v>
       </c>
       <c r="M7" t="n">
-        <v>4.219863745086339</v>
+        <v>4.199686377440052</v>
       </c>
       <c r="N7" t="n">
-        <v>103.5171266415129</v>
+        <v>102.8385211136634</v>
       </c>
       <c r="O7" t="n">
-        <v>10.17433666837858</v>
+        <v>10.14093295085139</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8588212670476</v>
+        <v>376.8712446519681</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33445,28 +33657,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04468271199991279</v>
+        <v>0.04424051863680493</v>
       </c>
       <c r="J8" t="n">
+        <v>306</v>
+      </c>
+      <c r="K8" t="n">
         <v>304</v>
       </c>
-      <c r="K8" t="n">
-        <v>302</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.001260225858866315</v>
+        <v>0.001254823106584091</v>
       </c>
       <c r="M8" t="n">
-        <v>6.01125800299714</v>
+        <v>5.976133237141195</v>
       </c>
       <c r="N8" t="n">
-        <v>84.82921804854664</v>
+        <v>84.27424941015775</v>
       </c>
       <c r="O8" t="n">
-        <v>9.210277848607317</v>
+        <v>9.180100729848107</v>
       </c>
       <c r="P8" t="n">
-        <v>372.9070116576199</v>
+        <v>372.911685890293</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33523,28 +33735,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02418880114085572</v>
+        <v>-0.03266960778978389</v>
       </c>
       <c r="J9" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K9" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002418323109567577</v>
+        <v>0.000447141567260223</v>
       </c>
       <c r="M9" t="n">
-        <v>7.844481361153367</v>
+        <v>7.834320505240155</v>
       </c>
       <c r="N9" t="n">
-        <v>130.5115305093009</v>
+        <v>129.8977221694291</v>
       </c>
       <c r="O9" t="n">
-        <v>11.42416432433029</v>
+        <v>11.39726818888759</v>
       </c>
       <c r="P9" t="n">
-        <v>370.3489329859125</v>
+        <v>370.4382048810846</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33601,28 +33813,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3590827392419589</v>
+        <v>-0.3642566174466654</v>
       </c>
       <c r="J10" t="n">
+        <v>306</v>
+      </c>
+      <c r="K10" t="n">
         <v>304</v>
       </c>
-      <c r="K10" t="n">
-        <v>302</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.04933896010849514</v>
+        <v>0.05142767463941089</v>
       </c>
       <c r="M10" t="n">
-        <v>8.208074109161906</v>
+        <v>8.177023671575441</v>
       </c>
       <c r="N10" t="n">
-        <v>131.6485364016042</v>
+        <v>130.873193994286</v>
       </c>
       <c r="O10" t="n">
-        <v>11.4738196082039</v>
+        <v>11.43998225498126</v>
       </c>
       <c r="P10" t="n">
-        <v>366.029283052308</v>
+        <v>366.0842848475595</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33679,28 +33891,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02364259181563802</v>
+        <v>-0.02797480236590338</v>
       </c>
       <c r="J11" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K11" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003427824297445037</v>
+        <v>0.0004871256720044848</v>
       </c>
       <c r="M11" t="n">
-        <v>6.145876708973196</v>
+        <v>6.119996232628281</v>
       </c>
       <c r="N11" t="n">
-        <v>85.47633697034323</v>
+        <v>84.97268393940453</v>
       </c>
       <c r="O11" t="n">
-        <v>9.245341365809228</v>
+        <v>9.218062916871665</v>
       </c>
       <c r="P11" t="n">
-        <v>355.1636088615049</v>
+        <v>355.2100716993363</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33757,28 +33969,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1182999761177228</v>
+        <v>0.113250890369675</v>
       </c>
       <c r="J12" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K12" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02304723149698928</v>
+        <v>0.02142952761180927</v>
       </c>
       <c r="M12" t="n">
-        <v>4.326825669951313</v>
+        <v>4.321282715905624</v>
       </c>
       <c r="N12" t="n">
-        <v>32.11742455321296</v>
+        <v>31.99619702060392</v>
       </c>
       <c r="O12" t="n">
-        <v>5.667223707708472</v>
+        <v>5.656518100439873</v>
       </c>
       <c r="P12" t="n">
-        <v>351.4066371793978</v>
+        <v>351.4595051649501</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33835,28 +34047,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2016688371616157</v>
+        <v>0.1942683962419198</v>
       </c>
       <c r="J13" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K13" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09746112748853608</v>
+        <v>0.09158913815343905</v>
       </c>
       <c r="M13" t="n">
-        <v>3.450287950278434</v>
+        <v>3.45866529929401</v>
       </c>
       <c r="N13" t="n">
-        <v>20.39053721446971</v>
+        <v>20.44929116467015</v>
       </c>
       <c r="O13" t="n">
-        <v>4.515588246781332</v>
+        <v>4.52208924775597</v>
       </c>
       <c r="P13" t="n">
-        <v>348.4974499947919</v>
+        <v>348.5749354199299</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33913,28 +34125,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1430833634463984</v>
+        <v>0.1396146272554357</v>
       </c>
       <c r="J14" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K14" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05039336663271865</v>
+        <v>0.04871445405037489</v>
       </c>
       <c r="M14" t="n">
-        <v>3.634522339948941</v>
+        <v>3.628771756421715</v>
       </c>
       <c r="N14" t="n">
-        <v>20.88647941397336</v>
+        <v>20.79459677147642</v>
       </c>
       <c r="O14" t="n">
-        <v>4.570172799137179</v>
+        <v>4.560109293808255</v>
       </c>
       <c r="P14" t="n">
-        <v>349.1654807511667</v>
+        <v>349.2017970389065</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33991,28 +34203,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2714899889203443</v>
+        <v>0.2657062446538141</v>
       </c>
       <c r="J15" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K15" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1738973501316995</v>
+        <v>0.1690875115383901</v>
       </c>
       <c r="M15" t="n">
-        <v>3.435850620711106</v>
+        <v>3.441332327155652</v>
       </c>
       <c r="N15" t="n">
-        <v>18.95681123013166</v>
+        <v>18.95321456296898</v>
       </c>
       <c r="O15" t="n">
-        <v>4.353942033391311</v>
+        <v>4.353528978078472</v>
       </c>
       <c r="P15" t="n">
-        <v>349.4879290406444</v>
+        <v>349.5484845034526</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34069,28 +34281,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3372865621157163</v>
+        <v>0.3323315350087228</v>
       </c>
       <c r="J16" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K16" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2353360363153097</v>
+        <v>0.2320104047076131</v>
       </c>
       <c r="M16" t="n">
-        <v>3.28605948242591</v>
+        <v>3.291113692157971</v>
       </c>
       <c r="N16" t="n">
-        <v>20.01229340263636</v>
+        <v>19.97223117875517</v>
       </c>
       <c r="O16" t="n">
-        <v>4.473510188055501</v>
+        <v>4.469030227997475</v>
       </c>
       <c r="P16" t="n">
-        <v>351.609127216094</v>
+        <v>351.6610045543754</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34147,28 +34359,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4493023594229656</v>
+        <v>0.4444997113916731</v>
       </c>
       <c r="J17" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K17" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3561352692905304</v>
+        <v>0.3538108218749234</v>
       </c>
       <c r="M17" t="n">
-        <v>3.364522856512767</v>
+        <v>3.364862057955609</v>
       </c>
       <c r="N17" t="n">
-        <v>19.75939504125492</v>
+        <v>19.71365434639733</v>
       </c>
       <c r="O17" t="n">
-        <v>4.445154107705932</v>
+        <v>4.440006120085571</v>
       </c>
       <c r="P17" t="n">
-        <v>351.0446946119967</v>
+        <v>351.0949777270006</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34225,28 +34437,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5469515810873872</v>
+        <v>0.542414274304221</v>
       </c>
       <c r="J18" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K18" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4380850051815894</v>
+        <v>0.4369481495259527</v>
       </c>
       <c r="M18" t="n">
-        <v>3.612841734638005</v>
+        <v>3.612650910880788</v>
       </c>
       <c r="N18" t="n">
-        <v>20.77430924300512</v>
+        <v>20.71172677729347</v>
       </c>
       <c r="O18" t="n">
-        <v>4.557884294604802</v>
+        <v>4.551013818622557</v>
       </c>
       <c r="P18" t="n">
-        <v>346.4686084493709</v>
+        <v>346.5161145246752</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34303,28 +34515,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5732551796425855</v>
+        <v>0.5677820850137664</v>
       </c>
       <c r="J19" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K19" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4104654020336098</v>
+        <v>0.4085890594354773</v>
       </c>
       <c r="M19" t="n">
-        <v>4.058770630397942</v>
+        <v>4.062055734933981</v>
       </c>
       <c r="N19" t="n">
-        <v>25.55320098820901</v>
+        <v>25.4918640696554</v>
       </c>
       <c r="O19" t="n">
-        <v>5.055017407310188</v>
+        <v>5.048946827770659</v>
       </c>
       <c r="P19" t="n">
-        <v>347.3238173067427</v>
+        <v>347.3811219275146</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34381,28 +34593,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5893502144809716</v>
+        <v>0.5841995749841096</v>
       </c>
       <c r="J20" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K20" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L20" t="n">
-        <v>0.381923066236081</v>
+        <v>0.3807365372236809</v>
       </c>
       <c r="M20" t="n">
-        <v>4.465881673716871</v>
+        <v>4.465406097377816</v>
       </c>
       <c r="N20" t="n">
-        <v>30.43197472885673</v>
+        <v>30.32557032461435</v>
       </c>
       <c r="O20" t="n">
-        <v>5.51651835208193</v>
+        <v>5.506865744197361</v>
       </c>
       <c r="P20" t="n">
-        <v>352.2835902364554</v>
+        <v>352.3375203730639</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34459,28 +34671,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6307782160177589</v>
+        <v>0.6256184020046525</v>
       </c>
       <c r="J21" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K21" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3710097012197158</v>
+        <v>0.3702147453175354</v>
       </c>
       <c r="M21" t="n">
-        <v>5.09994270901581</v>
+        <v>5.094347382549163</v>
       </c>
       <c r="N21" t="n">
-        <v>36.51982176385415</v>
+        <v>36.37419643281859</v>
       </c>
       <c r="O21" t="n">
-        <v>6.043163224988562</v>
+        <v>6.031102422676852</v>
       </c>
       <c r="P21" t="n">
-        <v>355.3132216021849</v>
+        <v>355.3672472735802</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34537,28 +34749,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5455427804946609</v>
+        <v>0.5314952493520563</v>
       </c>
       <c r="J22" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K22" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2174221720173944</v>
+        <v>0.2092906879547326</v>
       </c>
       <c r="M22" t="n">
-        <v>6.481888832364252</v>
+        <v>6.517800003212376</v>
       </c>
       <c r="N22" t="n">
-        <v>57.99598513754246</v>
+        <v>58.30439922069374</v>
       </c>
       <c r="O22" t="n">
-        <v>7.615509512668372</v>
+        <v>7.635731741011711</v>
       </c>
       <c r="P22" t="n">
-        <v>352.5616974064282</v>
+        <v>352.7087885544305</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34615,28 +34827,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9691361900327984</v>
+        <v>0.955771955262767</v>
       </c>
       <c r="J23" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K23" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5369384719736807</v>
+        <v>0.5303795308781518</v>
       </c>
       <c r="M23" t="n">
-        <v>5.379130353779282</v>
+        <v>5.410586966989724</v>
       </c>
       <c r="N23" t="n">
-        <v>43.85310975591614</v>
+        <v>44.18800882465493</v>
       </c>
       <c r="O23" t="n">
-        <v>6.622168055547681</v>
+        <v>6.647406172685322</v>
       </c>
       <c r="P23" t="n">
-        <v>343.050944914693</v>
+        <v>343.190877951876</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34693,28 +34905,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6716758866217404</v>
+        <v>0.6622059938344227</v>
       </c>
       <c r="J24" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K24" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4168331860356047</v>
+        <v>0.4114960646514764</v>
       </c>
       <c r="M24" t="n">
-        <v>4.85272491005805</v>
+        <v>4.867112794027684</v>
       </c>
       <c r="N24" t="n">
-        <v>34.1717030171167</v>
+        <v>34.26143134428185</v>
       </c>
       <c r="O24" t="n">
-        <v>5.845656765250308</v>
+        <v>5.853326519534157</v>
       </c>
       <c r="P24" t="n">
-        <v>354.3176004722528</v>
+        <v>354.4167602876792</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34771,28 +34983,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.694290688464316</v>
+        <v>0.6833142470050934</v>
       </c>
       <c r="J25" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K25" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4420883922128643</v>
+        <v>0.4349328649872772</v>
       </c>
       <c r="M25" t="n">
-        <v>4.782028501464905</v>
+        <v>4.795422291331686</v>
       </c>
       <c r="N25" t="n">
-        <v>32.93484028575133</v>
+        <v>33.14014296226723</v>
       </c>
       <c r="O25" t="n">
-        <v>5.738888419001657</v>
+        <v>5.756747602793371</v>
       </c>
       <c r="P25" t="n">
-        <v>361.7630667611963</v>
+        <v>361.8780016910218</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34849,28 +35061,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5848198039138436</v>
+        <v>0.5733249821487754</v>
       </c>
       <c r="J26" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K26" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3857350328289232</v>
+        <v>0.3763731461661275</v>
       </c>
       <c r="M26" t="n">
-        <v>4.35477112304746</v>
+        <v>4.383712532151592</v>
       </c>
       <c r="N26" t="n">
-        <v>29.48678343279538</v>
+        <v>29.75387359635577</v>
       </c>
       <c r="O26" t="n">
-        <v>5.430173425664726</v>
+        <v>5.454711137755671</v>
       </c>
       <c r="P26" t="n">
-        <v>347.3392361514299</v>
+        <v>347.4595969185627</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34927,28 +35139,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3973836352996605</v>
+        <v>0.3874157072157938</v>
       </c>
       <c r="J27" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K27" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2513301816062077</v>
+        <v>0.2422593689205697</v>
       </c>
       <c r="M27" t="n">
-        <v>3.933173693931341</v>
+        <v>3.961480931962844</v>
       </c>
       <c r="N27" t="n">
-        <v>25.46726058578954</v>
+        <v>25.64661460489644</v>
       </c>
       <c r="O27" t="n">
-        <v>5.046509742959934</v>
+        <v>5.064248671313094</v>
       </c>
       <c r="P27" t="n">
-        <v>345.1936382179094</v>
+        <v>345.2980112102618</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35005,28 +35217,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.232605184324963</v>
+        <v>0.2228791079763912</v>
       </c>
       <c r="J28" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K28" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L28" t="n">
-        <v>0.09714786642514284</v>
+        <v>0.09019421174080711</v>
       </c>
       <c r="M28" t="n">
-        <v>4.062521567814516</v>
+        <v>4.083533087985179</v>
       </c>
       <c r="N28" t="n">
-        <v>27.22317260213058</v>
+        <v>27.37438384654207</v>
       </c>
       <c r="O28" t="n">
-        <v>5.217583023022305</v>
+        <v>5.232053501880698</v>
       </c>
       <c r="P28" t="n">
-        <v>360.8629479903412</v>
+        <v>360.9647871451089</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35083,28 +35295,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1067414638078689</v>
+        <v>0.09589161918895178</v>
       </c>
       <c r="J29" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K29" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0311378545051848</v>
+        <v>0.02514206810169495</v>
       </c>
       <c r="M29" t="n">
-        <v>3.315805173341084</v>
+        <v>3.353147116922431</v>
       </c>
       <c r="N29" t="n">
-        <v>19.19358967764864</v>
+        <v>19.4776805145872</v>
       </c>
       <c r="O29" t="n">
-        <v>4.381048924361452</v>
+        <v>4.41335252552832</v>
       </c>
       <c r="P29" t="n">
-        <v>372.2989456274483</v>
+        <v>372.412552179019</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35142,7 +35354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD305"/>
+  <dimension ref="A1:AD307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81113,6 +81325,310 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>-36.66820634088284,175.55785212790192</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>-36.66883521950195,175.5573771962967</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-36.669506112014716,175.55704870037096</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-36.67015003278258,175.556626230228</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-36.67082777567098,175.55632164824482</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-36.67148345641288,175.55601948609873</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-36.672162280694984,175.55580681516258</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-36.67286745933134,175.55559056403158</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-36.67357369605133,175.55536512265002</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-36.67428822169917,175.5552463278685</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-36.6750034767309,175.55513699544642</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-36.675718496072996,175.5550021306907</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-36.676439394467586,175.55494796165246</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-36.67715872064145,175.5548970656575</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-36.67788091174659,175.5548730076224</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-36.67860020260879,175.5549033157452</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>-36.679319001082604,175.55498327040456</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>-36.68003415009037,175.5550909104957</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>-36.680742893960435,175.55525416761296</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>-36.681442782835255,175.55543400975142</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>-36.68216237106105,175.5555464088187</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>-36.682854206748445,175.55579638843415</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>-36.683533518808254,175.5561009081607</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>-36.6841939003902,175.55639772035494</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>-36.684855287059186,175.55674663085446</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>-36.68545978606077,175.55724397987876</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>-36.685967352560226,175.5578914960617</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>-36.68632190607841,175.55866428255163</t>
+        </is>
+      </c>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-36.66821299148782,175.55787530481695</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>-36.66891732473826,175.5576633281517</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>-36.669506112014716,175.55704870037096</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-36.67014465170591,175.5566074775721</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-36.67082822913455,175.5563232285381</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-36.67148351895709,175.55601981250635</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-36.67216106998894,175.55579325380654</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-36.67286642888114,175.55557731665854</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-36.673573185147326,175.5553585545649</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-36.67428808314823,175.55524454667636</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-36.67500345075248,175.5551366614698</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-36.675719186621535,175.55501272127103</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-36.67644015087615,175.55496258328694</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-36.67715959974935,175.55491436748125</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>-36.6778812801063,175.55489324686786</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-36.67859929816149,175.55491882210035</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>-36.67931787718828,175.55499425525522</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>-36.680033071596625,175.55510145160963</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>-36.68074241460891,175.55525815005169</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>-36.6814417419746,175.55543968071552</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>-36.682164296765066,175.55553801821628</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>-36.682853392021485,175.5557999383335</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>-36.6835355186104,175.55609219470222</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>-36.68419761865407,175.55638839819068</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>-36.6848569418306,175.55674397762232</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>-36.68546147402868,175.5572413590627</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>-36.68596629459889,175.5578927116583</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>-36.68632227907664,175.55866396897667</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
